--- a/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Discagem_Smart Factory Agendamentos.xlsx
+++ b/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Discagem_Smart Factory Agendamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Agendamento_Smart_Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663D2984-3DBD-4499-9306-3035A15F7582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4540F173-456C-4E98-9FD0-4CA8C82E1F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{18287E13-523A-4B69-86E2-0C7AA7A14E38}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12978" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13731" uniqueCount="175">
   <si>
     <t>DATA</t>
   </si>
@@ -440,6 +440,111 @@
   </si>
   <si>
     <t>(22) 99704-5444</t>
+  </si>
+  <si>
+    <t>(21) 96496-4808</t>
+  </si>
+  <si>
+    <t>(21) 99351-8317</t>
+  </si>
+  <si>
+    <t>(21) 3799-0303</t>
+  </si>
+  <si>
+    <t>(21) 93799-0303</t>
+  </si>
+  <si>
+    <t>(24) 2231-2716</t>
+  </si>
+  <si>
+    <t>(22) 99999-3344</t>
+  </si>
+  <si>
+    <t>(21) 96412-1921</t>
+  </si>
+  <si>
+    <t>(22) 99279-3302</t>
+  </si>
+  <si>
+    <t>(21) 99043-7105</t>
+  </si>
+  <si>
+    <t>(21) 3449-9000</t>
+  </si>
+  <si>
+    <t>(21) 99954-9956</t>
+  </si>
+  <si>
+    <t>(21) 99971-6434</t>
+  </si>
+  <si>
+    <t>(24) 99842-8958</t>
+  </si>
+  <si>
+    <t>(21) 98142-5542</t>
+  </si>
+  <si>
+    <t>(21) 2502-0200</t>
+  </si>
+  <si>
+    <t>(21) 98496-8854</t>
+  </si>
+  <si>
+    <t>(21) 97504-0611</t>
+  </si>
+  <si>
+    <t>(21) 96423-1738</t>
+  </si>
+  <si>
+    <t>(21) 96448-2900</t>
+  </si>
+  <si>
+    <t>(24) 97403-5107</t>
+  </si>
+  <si>
+    <t>(24) 99279-1804</t>
+  </si>
+  <si>
+    <t>(21) 96411-3002</t>
+  </si>
+  <si>
+    <t>(21) 96459-2050</t>
+  </si>
+  <si>
+    <t>(21) 99210-9372</t>
+  </si>
+  <si>
+    <t>(22) 99944-4350</t>
+  </si>
+  <si>
+    <t>(21) 99386-3181</t>
+  </si>
+  <si>
+    <t>(21) 99757-7410</t>
+  </si>
+  <si>
+    <t>(24) 99994-2313</t>
+  </si>
+  <si>
+    <t>(22) 99826-2171</t>
+  </si>
+  <si>
+    <t>(22) 99760-7085</t>
+  </si>
+  <si>
+    <t>(22) 99815-4513</t>
+  </si>
+  <si>
+    <t>(24) 99909-7084</t>
+  </si>
+  <si>
+    <t>(21) 96770-6101</t>
+  </si>
+  <si>
+    <t>(21) 97123-0789</t>
+  </si>
+  <si>
+    <t>(22) 98802-7200</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCA3C27-62A6-41B6-A964-C148E02992FA}">
-  <dimension ref="A1:S1620"/>
+  <dimension ref="A1:S1714"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -68652,6 +68757,4016 @@
         <v>9.6759259259259264E-3</v>
       </c>
     </row>
+    <row r="1621" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1621" s="1">
+        <v>46224.38181712963</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1621">
+        <v>2749600618</v>
+      </c>
+      <c r="G1621" s="2">
+        <v>178463578981091</v>
+      </c>
+      <c r="H1621" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1621" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1621" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1621" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1621" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1621" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1621">
+        <v>16</v>
+      </c>
+      <c r="R1621" s="3">
+        <v>7.2569444444444443E-3</v>
+      </c>
+      <c r="S1621" s="3">
+        <v>6.9675925925925929E-3</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1622" s="1">
+        <v>46224.391643518517</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1622">
+        <v>2776875643</v>
+      </c>
+      <c r="G1622" s="2">
+        <v>178463663896621</v>
+      </c>
+      <c r="H1622" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1622" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1622" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1622" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1622" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1622">
+        <v>19</v>
+      </c>
+      <c r="R1622" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1622" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1623" s="1">
+        <v>46224.39230324074</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1623">
+        <v>2773118524</v>
+      </c>
+      <c r="G1623" s="2">
+        <v>178463669598241</v>
+      </c>
+      <c r="H1623" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1623" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1623" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1623" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1623" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1623" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1623">
+        <v>16</v>
+      </c>
+      <c r="R1623" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="S1623" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1624" s="1">
+        <v>46224.393564814818</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1624">
+        <v>2778155142</v>
+      </c>
+      <c r="G1624" s="2">
+        <v>1784636804101090</v>
+      </c>
+      <c r="H1624" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1624" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1624" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1624" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1624" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1624" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1624">
+        <v>16</v>
+      </c>
+      <c r="R1624" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="S1624" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1625" s="1">
+        <v>46224.393993055557</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1625">
+        <v>2778155179</v>
+      </c>
+      <c r="G1625" s="2">
+        <v>1784636841101970</v>
+      </c>
+      <c r="H1625" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1625" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1625" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1625" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1625" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1625" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1625">
+        <v>16</v>
+      </c>
+      <c r="R1625" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1625" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1626" s="1">
+        <v>46224.394444444442</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1626">
+        <v>1822627204</v>
+      </c>
+      <c r="G1626" s="2">
+        <v>1784636880102530</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1626" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1626" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1626" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1626" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1626">
+        <v>19</v>
+      </c>
+      <c r="R1626" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1626" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1627" s="1">
+        <v>46224.394641203704</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1627">
+        <v>2722627221</v>
+      </c>
+      <c r="G1627" s="2">
+        <v>1784636897103010</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1627" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1627" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1627" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1627">
+        <v>19</v>
+      </c>
+      <c r="R1627" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="S1627" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1628" s="1">
+        <v>46224.395486111112</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1628">
+        <v>2777515442</v>
+      </c>
+      <c r="G1628" s="2">
+        <v>1784636970105220</v>
+      </c>
+      <c r="H1628" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1628" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1628" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1628" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1628" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1628" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1628">
+        <v>16</v>
+      </c>
+      <c r="R1628" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="S1628" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1629" s="1">
+        <v>46224.396122685182</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1629">
+        <v>2777515497</v>
+      </c>
+      <c r="G1629" s="2">
+        <v>1784637025107290</v>
+      </c>
+      <c r="H1629" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1629" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1629" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1629" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1629" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1629" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1629">
+        <v>16</v>
+      </c>
+      <c r="R1629" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1629" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1630" s="1">
+        <v>46224.397916666669</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1630">
+        <v>1806949920</v>
+      </c>
+      <c r="G1630" s="2">
+        <v>1784637179111460</v>
+      </c>
+      <c r="H1630" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1630" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1630" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1630" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1630" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1630" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1630">
+        <v>16</v>
+      </c>
+      <c r="R1630" s="3">
+        <v>7.2800925925925923E-3</v>
+      </c>
+      <c r="S1630" s="3">
+        <v>7.1643518518518514E-3</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1631" s="1">
+        <v>46224.409687500003</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1631">
+        <v>2784631563</v>
+      </c>
+      <c r="G1631" s="2">
+        <v>1784638197141200</v>
+      </c>
+      <c r="H1631" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1631" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1631" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1631" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1631" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1631" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1631">
+        <v>16</v>
+      </c>
+      <c r="R1631" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1631" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1632" s="1">
+        <v>46224.410173611112</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1632">
+        <v>2784631605</v>
+      </c>
+      <c r="G1632" s="2">
+        <v>1784638239142200</v>
+      </c>
+      <c r="H1632" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1632" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1632" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1632" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1632" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1632" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1632">
+        <v>16</v>
+      </c>
+      <c r="R1632" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="S1632" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1633" s="1">
+        <v>46224.411168981482</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1633">
+        <v>2784631691</v>
+      </c>
+      <c r="G1633" s="2">
+        <v>1784638325144080</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1633" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1633" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1633" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1633" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1633" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1633">
+        <v>16</v>
+      </c>
+      <c r="R1633" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1633" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1634" s="1">
+        <v>46224.41238425926</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1634">
+        <v>2748760372</v>
+      </c>
+      <c r="G1634" s="2">
+        <v>1784638430146930</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1634" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1634" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1634" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1634" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1634">
+        <v>19</v>
+      </c>
+      <c r="R1634" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1634" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1635" s="1">
+        <v>46224.412523148145</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1635">
+        <v>2748760384</v>
+      </c>
+      <c r="G1635" s="2">
+        <v>1784638442147150</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1635" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1635" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1635" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1635">
+        <v>19</v>
+      </c>
+      <c r="R1635" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1635" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1636" s="1">
+        <v>46224.412719907406</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1636">
+        <v>2748760401</v>
+      </c>
+      <c r="G1636" s="2">
+        <v>1784638459147530</v>
+      </c>
+      <c r="H1636" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1636" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1636" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1636" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1636" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1636">
+        <v>19</v>
+      </c>
+      <c r="R1636" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1636" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1637" s="1">
+        <v>46224.414687500001</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1637">
+        <v>2777431953</v>
+      </c>
+      <c r="G1637" s="2">
+        <v>1784638629151830</v>
+      </c>
+      <c r="H1637" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1637" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1637" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1637" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1637" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1637" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1637">
+        <v>16</v>
+      </c>
+      <c r="R1637" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1637" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1638" s="1">
+        <v>46224.415208333332</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1638">
+        <v>2777431998</v>
+      </c>
+      <c r="G1638" s="2">
+        <v>1784638674153280</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1638" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1638" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1638" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1638" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1638" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1638">
+        <v>16</v>
+      </c>
+      <c r="R1638" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1638" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1639" s="1">
+        <v>46224.415636574071</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1639">
+        <v>2777432035</v>
+      </c>
+      <c r="G1639" s="2">
+        <v>1784638711155140</v>
+      </c>
+      <c r="H1639" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1639" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1639" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1639" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1639" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1639">
+        <v>19</v>
+      </c>
+      <c r="R1639" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1639" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1640" s="1">
+        <v>46224.417013888888</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1640">
+        <v>2775075956</v>
+      </c>
+      <c r="G1640" s="2">
+        <v>1784638830159910</v>
+      </c>
+      <c r="H1640" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1640" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1640" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1640" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1640" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1640">
+        <v>19</v>
+      </c>
+      <c r="R1640" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1640" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1641" s="1">
+        <v>46224.417187500003</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1641">
+        <v>2775075971</v>
+      </c>
+      <c r="G1641" s="2">
+        <v>1784638845160570</v>
+      </c>
+      <c r="H1641" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1641" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1641" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1641" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1641" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1641" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1641">
+        <v>16</v>
+      </c>
+      <c r="R1641" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1641" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1642" s="1">
+        <v>46224.417349537034</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1642">
+        <v>2775075985</v>
+      </c>
+      <c r="G1642" s="2">
+        <v>1784638859161340</v>
+      </c>
+      <c r="H1642" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1642" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1642" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1642" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1642" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1642">
+        <v>19</v>
+      </c>
+      <c r="R1642" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1642" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1643" s="1">
+        <v>46224.417569444442</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1643">
+        <v>1819137899</v>
+      </c>
+      <c r="G1643" s="2">
+        <v>1784638878162310</v>
+      </c>
+      <c r="H1643" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1643" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1643" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1643" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1643" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1643" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1643">
+        <v>16</v>
+      </c>
+      <c r="R1643" s="3">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="S1643" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1644" s="1">
+        <v>46224.420208333337</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1644">
+        <v>2784189083</v>
+      </c>
+      <c r="G1644" s="2">
+        <v>1784639106172390</v>
+      </c>
+      <c r="H1644" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1644" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1644" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1644" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1644" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1644">
+        <v>19</v>
+      </c>
+      <c r="R1644" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1644" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1645" s="1">
+        <v>46224.420520833337</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1645">
+        <v>2784189110</v>
+      </c>
+      <c r="G1645" s="2">
+        <v>1784639133173630</v>
+      </c>
+      <c r="H1645" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1645" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1645" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1645" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1645" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1645">
+        <v>19</v>
+      </c>
+      <c r="R1645" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1645" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1646" s="1">
+        <v>46224.420810185184</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1646">
+        <v>2784189135</v>
+      </c>
+      <c r="G1646" s="2">
+        <v>1784639158174940</v>
+      </c>
+      <c r="H1646" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1646" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1646" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1646" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1646" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1646">
+        <v>19</v>
+      </c>
+      <c r="R1646" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="S1646" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1647" s="1">
+        <v>46224.422662037039</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1647">
+        <v>2784355773</v>
+      </c>
+      <c r="G1647" s="2">
+        <v>1784639318180290</v>
+      </c>
+      <c r="H1647" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1647" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1647" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1647" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1647" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1647" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1647">
+        <v>16</v>
+      </c>
+      <c r="R1647" s="3">
+        <v>2.3958333333333331E-3</v>
+      </c>
+      <c r="S1647" s="3">
+        <v>2.3263888888888887E-3</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1648" s="1">
+        <v>46224.430636574078</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1648">
+        <v>2783068989</v>
+      </c>
+      <c r="G1648" s="2">
+        <v>1784640007198130</v>
+      </c>
+      <c r="H1648" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1648" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1648" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1648" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1648" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1648" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1648">
+        <v>16</v>
+      </c>
+      <c r="R1648" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S1648" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1649" s="1">
+        <v>46224.431030092594</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1649">
+        <v>2783069024</v>
+      </c>
+      <c r="G1649" s="2">
+        <v>1784640041199180</v>
+      </c>
+      <c r="H1649" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1649" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1649" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1649" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1649" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1649" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1649">
+        <v>16</v>
+      </c>
+      <c r="R1649" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="S1649" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1650" s="1">
+        <v>46224.432650462964</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1650">
+        <v>2766065744</v>
+      </c>
+      <c r="G1650" s="2">
+        <v>1784640181202920</v>
+      </c>
+      <c r="H1650" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1650" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1650" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1650" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1650" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1650">
+        <v>19</v>
+      </c>
+      <c r="R1650" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1650" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1651" s="1">
+        <v>46224.433055555557</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1651">
+        <v>2766065779</v>
+      </c>
+      <c r="G1651" s="2">
+        <v>1784640216203490</v>
+      </c>
+      <c r="H1651" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1651" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1651" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1651" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1651" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1651">
+        <v>19</v>
+      </c>
+      <c r="R1651" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1651" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1652" s="1">
+        <v>46224.43346064815</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1652">
+        <v>2766065814</v>
+      </c>
+      <c r="G1652" s="2">
+        <v>1784640251204360</v>
+      </c>
+      <c r="H1652" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1652" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1652" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1652" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1652" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1652">
+        <v>19</v>
+      </c>
+      <c r="R1652" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1652" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1653" s="1">
+        <v>46224.434918981482</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1653">
+        <v>2779871462</v>
+      </c>
+      <c r="G1653" s="2">
+        <v>1784640377207200</v>
+      </c>
+      <c r="H1653" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1653" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1653" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1653" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1653" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1653">
+        <v>19</v>
+      </c>
+      <c r="R1653" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="S1653" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1654" s="1">
+        <v>46224.43577546296</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1654">
+        <v>2779871536</v>
+      </c>
+      <c r="G1654" s="2">
+        <v>1784640451209020</v>
+      </c>
+      <c r="H1654" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1654" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1654" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1654" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1654" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1654">
+        <v>19</v>
+      </c>
+      <c r="R1654" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1654" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1655" s="1">
+        <v>46224.436886574076</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1655">
+        <v>1809660768</v>
+      </c>
+      <c r="G1655" s="2">
+        <v>1784640547212410</v>
+      </c>
+      <c r="H1655" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1655" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1655" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1655" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1655" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1655" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1655">
+        <v>16</v>
+      </c>
+      <c r="R1655" s="3">
+        <v>3.2638888888888891E-3</v>
+      </c>
+      <c r="S1655" s="3">
+        <v>3.2291666666666666E-3</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1656" s="1">
+        <v>46224.44023148148</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1656">
+        <v>2769609711</v>
+      </c>
+      <c r="G1656" s="2">
+        <v>1784640836219970</v>
+      </c>
+      <c r="H1656" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1656" t="s">
+        <v>155</v>
+      </c>
+      <c r="J1656" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1656" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1656" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1656" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1656">
+        <v>16</v>
+      </c>
+      <c r="R1656" s="3">
+        <v>1.3657407407407407E-3</v>
+      </c>
+      <c r="S1656" s="3">
+        <v>1.238425925925926E-3</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1657" s="1">
+        <v>46224.445069444446</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1657">
+        <v>2759681826</v>
+      </c>
+      <c r="G1657" s="2">
+        <v>1784641194227970</v>
+      </c>
+      <c r="H1657" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1657" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1657" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1657" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1657" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1657">
+        <v>19</v>
+      </c>
+      <c r="R1657" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1657" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1658" s="1">
+        <v>46224.445729166669</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1658">
+        <v>2759681893</v>
+      </c>
+      <c r="G1658" s="2">
+        <v>1784641261229650</v>
+      </c>
+      <c r="H1658" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1658" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1658" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1658" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1658" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1658">
+        <v>19</v>
+      </c>
+      <c r="R1658" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1658" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1659" s="1">
+        <v>46224.446886574071</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1659">
+        <v>2759681994</v>
+      </c>
+      <c r="G1659" s="2">
+        <v>1784641362232150</v>
+      </c>
+      <c r="H1659" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1659" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1659" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1659" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1659" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1659">
+        <v>19</v>
+      </c>
+      <c r="R1659" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1659" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1660" s="1">
+        <v>46224.44767361111</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1660">
+        <v>2748873238</v>
+      </c>
+      <c r="G1660" s="2">
+        <v>1784641479235970</v>
+      </c>
+      <c r="H1660" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1660" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1660" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1660" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1660" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1660">
+        <v>19</v>
+      </c>
+      <c r="R1660" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1660" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1661" s="1">
+        <v>46224.447997685187</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1661">
+        <v>2748873266</v>
+      </c>
+      <c r="G1661" s="2">
+        <v>1784641507236650</v>
+      </c>
+      <c r="H1661" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1661" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1661" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1661" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1661" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1661">
+        <v>19</v>
+      </c>
+      <c r="R1661" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1661" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1662" s="1">
+        <v>46224.448414351849</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1662">
+        <v>2748873302</v>
+      </c>
+      <c r="G1662" s="2">
+        <v>1784641543238310</v>
+      </c>
+      <c r="H1662" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1662" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1662" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1662" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1662" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1662">
+        <v>19</v>
+      </c>
+      <c r="R1662" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S1662" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1663" s="1">
+        <v>46224.449490740742</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1663">
+        <v>2749124557</v>
+      </c>
+      <c r="G1663" s="2">
+        <v>1784641636240620</v>
+      </c>
+      <c r="H1663" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1663" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1663" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1663" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1663" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1663" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1663">
+        <v>16</v>
+      </c>
+      <c r="R1663" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1663" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1664" s="1">
+        <v>46224.44972222222</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1664">
+        <v>2749124577</v>
+      </c>
+      <c r="G1664" s="2">
+        <v>1784641656241330</v>
+      </c>
+      <c r="H1664" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1664" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1664" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1664" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1664" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1664" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1664">
+        <v>16</v>
+      </c>
+      <c r="R1664" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1664" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1665" s="1">
+        <v>46224.450127314813</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1665">
+        <v>2749124612</v>
+      </c>
+      <c r="G1665" s="2">
+        <v>1784641691242320</v>
+      </c>
+      <c r="H1665" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1665" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1665" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1665" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1665" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1665">
+        <v>19</v>
+      </c>
+      <c r="R1665" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1665" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1666" s="1">
+        <v>46224.45988425926</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1666">
+        <v>2758677665</v>
+      </c>
+      <c r="G1666" s="2">
+        <v>1784642534269410</v>
+      </c>
+      <c r="H1666" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1666" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1666" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1666" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1666" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1666" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1666">
+        <v>16</v>
+      </c>
+      <c r="R1666" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1666" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1667" s="1">
+        <v>46224.460127314815</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1667">
+        <v>2758677686</v>
+      </c>
+      <c r="G1667" s="2">
+        <v>1784642555270430</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1667" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1667" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1667" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1667" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1667" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1667">
+        <v>16</v>
+      </c>
+      <c r="R1667" s="3">
+        <v>4.1087962962962962E-3</v>
+      </c>
+      <c r="S1667" s="3">
+        <v>3.7731481481481483E-3</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1668" s="1">
+        <v>46224.464548611111</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1668">
+        <v>2758678069</v>
+      </c>
+      <c r="G1668" s="2">
+        <v>1784642937283880</v>
+      </c>
+      <c r="H1668" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1668" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1668" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1668" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1668" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1668">
+        <v>19</v>
+      </c>
+      <c r="R1668" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1668" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1669" s="1">
+        <v>46224.465150462966</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1669">
+        <v>2758678120</v>
+      </c>
+      <c r="G1669" s="2">
+        <v>1784642989286010</v>
+      </c>
+      <c r="H1669" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1669" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1669" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1669" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1669" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1669" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1669">
+        <v>16</v>
+      </c>
+      <c r="R1669" s="3">
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="S1669" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1670" s="1">
+        <v>46224.471863425926</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1670">
+        <v>2777435397</v>
+      </c>
+      <c r="G1670" s="2">
+        <v>1784643569298880</v>
+      </c>
+      <c r="H1670" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1670" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1670" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1670" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1670" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1670">
+        <v>19</v>
+      </c>
+      <c r="R1670" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1670" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1671" s="1">
+        <v>46224.471990740742</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1671">
+        <v>2777435408</v>
+      </c>
+      <c r="G1671" s="2">
+        <v>1784643580299120</v>
+      </c>
+      <c r="H1671" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1671" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1671" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1671" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1671" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1671">
+        <v>19</v>
+      </c>
+      <c r="R1671" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1671" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1672" s="1">
+        <v>46224.472118055557</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1672">
+        <v>2777435419</v>
+      </c>
+      <c r="G1672" s="2">
+        <v>1784643591299300</v>
+      </c>
+      <c r="H1672" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1672" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1672" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1672" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1672" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1672">
+        <v>19</v>
+      </c>
+      <c r="R1672" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1672" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1673" s="1">
+        <v>46224.47315972222</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1673">
+        <v>2748756704</v>
+      </c>
+      <c r="G1673" s="2">
+        <v>1784643681301110</v>
+      </c>
+      <c r="H1673" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1673" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1673" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1673" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1673" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1673" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1673">
+        <v>16</v>
+      </c>
+      <c r="R1673" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1673" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1674" s="1">
+        <v>46224.473402777781</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1674">
+        <v>2748756725</v>
+      </c>
+      <c r="G1674" s="2">
+        <v>1784643702301620</v>
+      </c>
+      <c r="H1674" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1674" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1674" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1674" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1674" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1674" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1674">
+        <v>16</v>
+      </c>
+      <c r="R1674" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1674" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1675" s="1">
+        <v>46224.473761574074</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1675">
+        <v>2748756756</v>
+      </c>
+      <c r="G1675" s="2">
+        <v>1784643733302200</v>
+      </c>
+      <c r="H1675" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1675" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1675" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1675" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1675" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1675">
+        <v>19</v>
+      </c>
+      <c r="R1675" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1675" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1676" s="1">
+        <v>46224.475462962961</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1676">
+        <v>2749235891</v>
+      </c>
+      <c r="G1676" s="2">
+        <v>1784643820304130</v>
+      </c>
+      <c r="H1676" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1676" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1676" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1676" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1676" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1676">
+        <v>19</v>
+      </c>
+      <c r="R1676" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1676" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1677" s="1">
+        <v>46224.475543981483</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1677">
+        <v>2749235958</v>
+      </c>
+      <c r="G1677" s="2">
+        <v>1784643887305060</v>
+      </c>
+      <c r="H1677" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1677" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1677" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1677" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1677" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1677" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1677">
+        <v>16</v>
+      </c>
+      <c r="R1677" s="3">
+        <v>1.1921296296296296E-3</v>
+      </c>
+      <c r="S1677" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1678" s="1">
+        <v>46224.478425925925</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1678">
+        <v>2776753529</v>
+      </c>
+      <c r="G1678" s="2">
+        <v>1784644136309440</v>
+      </c>
+      <c r="H1678" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1678" t="s">
+        <v>163</v>
+      </c>
+      <c r="J1678" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1678" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1678" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1678" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1678">
+        <v>16</v>
+      </c>
+      <c r="R1678" s="3">
+        <v>6.9560185185185185E-3</v>
+      </c>
+      <c r="S1678" s="3">
+        <v>6.7824074074074071E-3</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1679" s="1">
+        <v>46224.489432870374</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1679">
+        <v>2784089459</v>
+      </c>
+      <c r="G1679" s="2">
+        <v>1784645087336690</v>
+      </c>
+      <c r="H1679" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1679" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1679" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1679" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1679" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1679" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1679">
+        <v>16</v>
+      </c>
+      <c r="R1679" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1679" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1680" s="1">
+        <v>46224.489675925928</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1680">
+        <v>2784089480</v>
+      </c>
+      <c r="G1680" s="2">
+        <v>1784645108337310</v>
+      </c>
+      <c r="H1680" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1680" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1680" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1680" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1680" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1680" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1680">
+        <v>16</v>
+      </c>
+      <c r="R1680" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1680" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1681" s="1">
+        <v>46224.489872685182</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1681">
+        <v>2784089497</v>
+      </c>
+      <c r="G1681" s="2">
+        <v>1784645125337850</v>
+      </c>
+      <c r="H1681" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1681" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1681" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1681" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1681" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1681" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1681">
+        <v>16</v>
+      </c>
+      <c r="R1681" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1681" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1682" s="1">
+        <v>46224.491493055553</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1682">
+        <v>2764631276</v>
+      </c>
+      <c r="G1682" s="2">
+        <v>1784645265341600</v>
+      </c>
+      <c r="H1682" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1682" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1682" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1682" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1682" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1682">
+        <v>19</v>
+      </c>
+      <c r="R1682" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1682" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1683" s="1">
+        <v>46224.491828703707</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1683">
+        <v>2764631305</v>
+      </c>
+      <c r="G1683" s="2">
+        <v>1784645294342300</v>
+      </c>
+      <c r="H1683" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1683" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1683" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1683" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1683" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1683">
+        <v>19</v>
+      </c>
+      <c r="R1683" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1683" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1684" s="1">
+        <v>46224.491979166669</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1684">
+        <v>2764631318</v>
+      </c>
+      <c r="G1684" s="2">
+        <v>1784645307342720</v>
+      </c>
+      <c r="H1684" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1684" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1684" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1684" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1684" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1684">
+        <v>19</v>
+      </c>
+      <c r="R1684" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1684" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1685" s="1">
+        <v>46224.492418981485</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1685">
+        <v>2764631356</v>
+      </c>
+      <c r="G1685" s="2">
+        <v>1784645345343660</v>
+      </c>
+      <c r="H1685" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1685" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1685" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1685" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1685" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1685" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1685">
+        <v>16</v>
+      </c>
+      <c r="R1685" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="S1685" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1686" s="1">
+        <v>46224.494120370371</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1686">
+        <v>2778508694</v>
+      </c>
+      <c r="G1686" s="2">
+        <v>1784645492347250</v>
+      </c>
+      <c r="H1686" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1686" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1686" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1686" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1686" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1686">
+        <v>19</v>
+      </c>
+      <c r="R1686" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1686" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1687" s="1">
+        <v>46224.494641203702</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1687">
+        <v>2778508739</v>
+      </c>
+      <c r="G1687" s="2">
+        <v>1784645537347990</v>
+      </c>
+      <c r="H1687" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1687" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1687" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1687" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1687" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1687" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1687">
+        <v>16</v>
+      </c>
+      <c r="R1687" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1687" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1688" s="1">
+        <v>46224.495937500003</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1688">
+        <v>2782223028</v>
+      </c>
+      <c r="G1688" s="2">
+        <v>1784645597349400</v>
+      </c>
+      <c r="H1688" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1688" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1688" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1688" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1688" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1688">
+        <v>19</v>
+      </c>
+      <c r="R1688" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1688" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1689" s="1">
+        <v>46224.496006944442</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1689">
+        <v>2782223086</v>
+      </c>
+      <c r="G1689" s="2">
+        <v>1784645655350320</v>
+      </c>
+      <c r="H1689" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1689" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1689" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1689" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1689" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1689">
+        <v>19</v>
+      </c>
+      <c r="R1689" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1689" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1690" s="1">
+        <v>46224.497442129628</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1690">
+        <v>2784588116</v>
+      </c>
+      <c r="G1690" s="2">
+        <v>1784645779353380</v>
+      </c>
+      <c r="H1690" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1690" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1690" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1690" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1690" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1690" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1690">
+        <v>16</v>
+      </c>
+      <c r="R1690" s="3">
+        <v>4.363425925925926E-3</v>
+      </c>
+      <c r="S1690" s="3">
+        <v>4.2013888888888891E-3</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1691" s="1">
+        <v>46224.504166666666</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1691">
+        <v>2784257287</v>
+      </c>
+      <c r="G1691" s="2">
+        <v>1784646360365520</v>
+      </c>
+      <c r="H1691" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1691" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1691" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1691" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1691" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1691" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1691">
+        <v>16</v>
+      </c>
+      <c r="R1691" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1691" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1692" s="1">
+        <v>46224.504618055558</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1692">
+        <v>2784257326</v>
+      </c>
+      <c r="G1692" s="2">
+        <v>1784646399366660</v>
+      </c>
+      <c r="H1692" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1692" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1692" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1692" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1692" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1692" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1692">
+        <v>16</v>
+      </c>
+      <c r="R1692" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1692" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1693" s="1">
+        <v>46224.505439814813</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1693">
+        <v>2782908663</v>
+      </c>
+      <c r="G1693" s="2">
+        <v>1784646470368580</v>
+      </c>
+      <c r="H1693" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1693" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1693" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1693" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1693" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1693" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1693">
+        <v>16</v>
+      </c>
+      <c r="R1693" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1693" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1694" s="1">
+        <v>46224.505648148152</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1694">
+        <v>2782908681</v>
+      </c>
+      <c r="G1694" s="2">
+        <v>1784646488368970</v>
+      </c>
+      <c r="H1694" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1694" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1694" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1694" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1694" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1694" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1694">
+        <v>16</v>
+      </c>
+      <c r="R1694" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1694" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1695" s="1">
+        <v>46224.505833333336</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1695">
+        <v>2782908697</v>
+      </c>
+      <c r="G1695" s="2">
+        <v>1784646504369440</v>
+      </c>
+      <c r="H1695" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1695" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1695" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1695" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1695" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1695" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1695">
+        <v>16</v>
+      </c>
+      <c r="R1695" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1695" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1696" s="1">
+        <v>46224.506689814814</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1696">
+        <v>2782253686</v>
+      </c>
+      <c r="G1696" s="2">
+        <v>1784646578371160</v>
+      </c>
+      <c r="H1696" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1696" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1696" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1696" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1696" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1696" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1696">
+        <v>16</v>
+      </c>
+      <c r="R1696" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1696" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1697" s="1">
+        <v>46224.507256944446</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1697">
+        <v>2782253734</v>
+      </c>
+      <c r="G1697" s="2">
+        <v>1784646627372620</v>
+      </c>
+      <c r="H1697" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1697" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1697" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1697" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1697" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1697" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1697">
+        <v>16</v>
+      </c>
+      <c r="R1697" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1697" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1698" s="1">
+        <v>46224.507962962962</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1698">
+        <v>2782253795</v>
+      </c>
+      <c r="G1698" s="2">
+        <v>1784646688374220</v>
+      </c>
+      <c r="H1698" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1698" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1698" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1698" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1698" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1698" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1698">
+        <v>16</v>
+      </c>
+      <c r="R1698" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1698" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1699" s="1">
+        <v>46224.514131944445</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1699">
+        <v>2782801706</v>
+      </c>
+      <c r="G1699" s="2">
+        <v>1784647171387410</v>
+      </c>
+      <c r="H1699" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1699" t="s">
+        <v>170</v>
+      </c>
+      <c r="J1699" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1699" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1699" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1699">
+        <v>19</v>
+      </c>
+      <c r="R1699" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1699" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1700" s="1">
+        <v>46224.514224537037</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1700">
+        <v>2782801764</v>
+      </c>
+      <c r="G1700" s="2">
+        <v>1784647229388640</v>
+      </c>
+      <c r="H1700" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1700" t="s">
+        <v>170</v>
+      </c>
+      <c r="J1700" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1700" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1700" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1700">
+        <v>19</v>
+      </c>
+      <c r="R1700" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="S1700" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1701" s="1">
+        <v>46224.516458333332</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1701">
+        <v>2783744530</v>
+      </c>
+      <c r="G1701" s="2">
+        <v>1784647422394210</v>
+      </c>
+      <c r="H1701" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1701" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1701" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1701" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1701" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1701" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1701">
+        <v>16</v>
+      </c>
+      <c r="R1701" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1701" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1702" s="1">
+        <v>46224.516898148147</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1702">
+        <v>2783744568</v>
+      </c>
+      <c r="G1702" s="2">
+        <v>1784647460395280</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1702" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1702" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1702" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1702" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1702" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1702">
+        <v>16</v>
+      </c>
+      <c r="R1702" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="S1702" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1703" s="1">
+        <v>46224.518483796295</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1703">
+        <v>2749172325</v>
+      </c>
+      <c r="G1703" s="2">
+        <v>1784647597399200</v>
+      </c>
+      <c r="H1703" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1703" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1703" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1703" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1703" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1703">
+        <v>19</v>
+      </c>
+      <c r="R1703" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="S1703" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1704" s="1">
+        <v>46224.519236111111</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1704">
+        <v>2749172390</v>
+      </c>
+      <c r="G1704" s="2">
+        <v>1784647662400760</v>
+      </c>
+      <c r="H1704" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1704" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1704" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1704" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1704" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1704">
+        <v>19</v>
+      </c>
+      <c r="R1704" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="S1704" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1705" s="1">
+        <v>46224.521527777775</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1705">
+        <v>2752353982</v>
+      </c>
+      <c r="G1705" s="2">
+        <v>1784647860405320</v>
+      </c>
+      <c r="H1705" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1705" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1705" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1705" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1705" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1705">
+        <v>19</v>
+      </c>
+      <c r="R1705" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1705" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1706" s="1">
+        <v>46224.522060185183</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1706">
+        <v>2752354028</v>
+      </c>
+      <c r="G1706" s="2">
+        <v>1784647906406070</v>
+      </c>
+      <c r="H1706" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1706" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1706" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1706" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1706" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1706" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1706">
+        <v>16</v>
+      </c>
+      <c r="R1706" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1706" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1707" s="1">
+        <v>46224.523692129631</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1707">
+        <v>2784001216</v>
+      </c>
+      <c r="G1707" s="2">
+        <v>1784648047409520</v>
+      </c>
+      <c r="H1707" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1707" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1707" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1707" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1707" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1707" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1707">
+        <v>16</v>
+      </c>
+      <c r="R1707" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S1707" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1708" s="1">
+        <v>46224.524224537039</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1708">
+        <v>2784001262</v>
+      </c>
+      <c r="G1708" s="2">
+        <v>1784648093410760</v>
+      </c>
+      <c r="H1708" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1708" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1708" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1708" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1708" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1708" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1708">
+        <v>16</v>
+      </c>
+      <c r="R1708" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1708" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1709" s="1">
+        <v>46224.525254629632</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1709">
+        <v>2755878992</v>
+      </c>
+      <c r="G1709" s="2">
+        <v>1784648182413060</v>
+      </c>
+      <c r="H1709" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1709" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1709" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1709" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1709" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1709">
+        <v>19</v>
+      </c>
+      <c r="R1709" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S1709" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1710" s="1">
+        <v>46224.525520833333</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1710">
+        <v>2755879015</v>
+      </c>
+      <c r="G1710" s="2">
+        <v>1784648205413700</v>
+      </c>
+      <c r="H1710" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1710" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1710" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1710" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1710" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1710" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1710">
+        <v>16</v>
+      </c>
+      <c r="R1710" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1710" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1711" s="1">
+        <v>46224.532037037039</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1711">
+        <v>2772675990</v>
+      </c>
+      <c r="G1711" s="2">
+        <v>1784648768427090</v>
+      </c>
+      <c r="H1711" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1711" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1711" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1711" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1711" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1711" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1711">
+        <v>16</v>
+      </c>
+      <c r="R1711" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1711" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1712" s="1">
+        <v>46224.532407407409</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1712">
+        <v>2772676022</v>
+      </c>
+      <c r="G1712" s="2">
+        <v>1784648800427740</v>
+      </c>
+      <c r="H1712" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1712" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1712" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1712" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1712" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1712" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1712">
+        <v>16</v>
+      </c>
+      <c r="R1712" s="3">
+        <v>2.3032407407407407E-3</v>
+      </c>
+      <c r="S1712" s="3">
+        <v>2.1990740740740742E-3</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1713" s="1">
+        <v>46224.537094907406</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1713">
+        <v>2777621407</v>
+      </c>
+      <c r="G1713" s="2">
+        <v>1784649205439110</v>
+      </c>
+      <c r="H1713" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1713" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1713" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1713" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1713" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1713" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1713">
+        <v>16</v>
+      </c>
+      <c r="R1713" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1713" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1714" s="1">
+        <v>46224.537476851852</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1714">
+        <v>2777621440</v>
+      </c>
+      <c r="G1714" s="2">
+        <v>1784649238439970</v>
+      </c>
+      <c r="H1714" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1714" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1714" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1714" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1714" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1714" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1714">
+        <v>16</v>
+      </c>
+      <c r="R1714" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1714" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Discagem_Smart Factory Agendamentos.xlsx
+++ b/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Discagem_Smart Factory Agendamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Agendamento_Smart_Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4540F173-456C-4E98-9FD0-4CA8C82E1F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EF9EF3-69B8-4E9B-80DE-D8A98903C5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{18287E13-523A-4B69-86E2-0C7AA7A14E38}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{18287E13-523A-4B69-86E2-0C7AA7A14E38}"/>
   </bookViews>
   <sheets>
     <sheet name="chamadas_10-07-2026_124916" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13731" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14541" uniqueCount="189">
   <si>
     <t>DATA</t>
   </si>
@@ -545,6 +545,48 @@
   </si>
   <si>
     <t>(22) 98802-7200</t>
+  </si>
+  <si>
+    <t>(22) 99711-1177</t>
+  </si>
+  <si>
+    <t>(22) 99792-0591</t>
+  </si>
+  <si>
+    <t>(21) 97612-0157</t>
+  </si>
+  <si>
+    <t>(21) 99880-1728</t>
+  </si>
+  <si>
+    <t>(24) 99814-4041</t>
+  </si>
+  <si>
+    <t>(21) 96841-8565</t>
+  </si>
+  <si>
+    <t>(21) 98476-3688</t>
+  </si>
+  <si>
+    <t>(21) 99671-6337</t>
+  </si>
+  <si>
+    <t>(21) 99151-7068</t>
+  </si>
+  <si>
+    <t>(21) 98808-0110</t>
+  </si>
+  <si>
+    <t>(21) 98586-4803</t>
+  </si>
+  <si>
+    <t>(22) 99853-3424</t>
+  </si>
+  <si>
+    <t>(21) 96565-4965</t>
+  </si>
+  <si>
+    <t>(21) 99640-2344</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCA3C27-62A6-41B6-A964-C148E02992FA}">
-  <dimension ref="A1:S1714"/>
+  <dimension ref="A1:S1815"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -72767,6 +72809,4267 @@
         <v>1.6203703703703703E-4</v>
       </c>
     </row>
+    <row r="1715" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1715" s="1">
+        <v>46225.588356481479</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1715">
+        <v>2781851233</v>
+      </c>
+      <c r="G1715" s="2">
+        <v>1784740034524550</v>
+      </c>
+      <c r="H1715" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1715" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1715" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1715" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1715" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1715">
+        <v>19</v>
+      </c>
+      <c r="R1715" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1715" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1716" s="1">
+        <v>46225.58861111111</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1716">
+        <v>2781851255</v>
+      </c>
+      <c r="G1716" s="2">
+        <v>1784740056524950</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1716" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1716" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1716" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1716" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1716">
+        <v>19</v>
+      </c>
+      <c r="R1716" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1716" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1717" s="1">
+        <v>46225.589131944442</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1717">
+        <v>2782660714</v>
+      </c>
+      <c r="G1717" s="2">
+        <v>1784740101525810</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1717" t="s">
+        <v>176</v>
+      </c>
+      <c r="J1717" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1717" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1717" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1717" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1717">
+        <v>16</v>
+      </c>
+      <c r="R1717" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1717" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1718" s="1">
+        <v>46225.590717592589</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1718">
+        <v>2760860416</v>
+      </c>
+      <c r="G1718" s="2">
+        <v>1784740238530320</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1718" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1718" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1718" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1718" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1718">
+        <v>19</v>
+      </c>
+      <c r="R1718" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="S1718" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1719" s="1">
+        <v>46225.591412037036</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1719">
+        <v>2783542047</v>
+      </c>
+      <c r="G1719" s="2">
+        <v>1784740298532420</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1719" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1719" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1719" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1719" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1719" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1719">
+        <v>16</v>
+      </c>
+      <c r="R1719" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="S1719" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1720" s="1">
+        <v>46225.592256944445</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1720">
+        <v>2782884424</v>
+      </c>
+      <c r="G1720" s="2">
+        <v>1784740359534660</v>
+      </c>
+      <c r="H1720" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1720" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1720" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1720" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1720" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1720">
+        <v>17</v>
+      </c>
+      <c r="R1720" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1720" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1721" s="1">
+        <v>46225.592476851853</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1721">
+        <v>2782884444</v>
+      </c>
+      <c r="G1721" s="2">
+        <v>1784740379535370</v>
+      </c>
+      <c r="H1721" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1721" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1721" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1721" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1721" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1721">
+        <v>17</v>
+      </c>
+      <c r="R1721" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1721" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1722" s="1">
+        <v>46225.59269675926</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1722">
+        <v>2753158995</v>
+      </c>
+      <c r="G1722" s="2">
+        <v>1784740409536460</v>
+      </c>
+      <c r="H1722" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1722" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1722" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1722" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1722" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1722">
+        <v>19</v>
+      </c>
+      <c r="R1722" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="S1722" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1723" s="1">
+        <v>46225.593668981484</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1723">
+        <v>2769504202</v>
+      </c>
+      <c r="G1723" s="2">
+        <v>1784740493539180</v>
+      </c>
+      <c r="H1723" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1723" t="s">
+        <v>181</v>
+      </c>
+      <c r="J1723" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1723" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1723" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1723">
+        <v>19</v>
+      </c>
+      <c r="R1723" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1723" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1724" s="1">
+        <v>46225.593946759262</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1724">
+        <v>2781456875</v>
+      </c>
+      <c r="G1724" s="2">
+        <v>1784740517540340</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1724" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1724" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1724" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1724" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1724">
+        <v>19</v>
+      </c>
+      <c r="R1724" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1724" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1725" s="1">
+        <v>46225.594513888886</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1725">
+        <v>2776257656</v>
+      </c>
+      <c r="G1725" s="2">
+        <v>1784740566542450</v>
+      </c>
+      <c r="H1725" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1725" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1725" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1725" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1725" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1725">
+        <v>19</v>
+      </c>
+      <c r="R1725" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1725" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1726" s="1">
+        <v>46225.595324074071</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1726">
+        <v>2772820767</v>
+      </c>
+      <c r="G1726" s="2">
+        <v>1784740636545140</v>
+      </c>
+      <c r="H1726" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1726" t="s">
+        <v>184</v>
+      </c>
+      <c r="J1726" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1726" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1726" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1726">
+        <v>19</v>
+      </c>
+      <c r="R1726" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1726" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1727" s="1">
+        <v>46225.595937500002</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1727">
+        <v>2770605513</v>
+      </c>
+      <c r="G1727" s="2">
+        <v>1784740689547450</v>
+      </c>
+      <c r="H1727" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1727" t="s">
+        <v>185</v>
+      </c>
+      <c r="J1727" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1727" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1727" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1727" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1727">
+        <v>16</v>
+      </c>
+      <c r="R1727" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1727" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1728" s="1">
+        <v>46225.596724537034</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1728">
+        <v>2783274203</v>
+      </c>
+      <c r="G1728" s="2">
+        <v>1784740757549790</v>
+      </c>
+      <c r="H1728" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1728" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1728" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1728" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1728" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1728" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1728">
+        <v>16</v>
+      </c>
+      <c r="R1728" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1728" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1729" s="1">
+        <v>46225.59716435185</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1729">
+        <v>2750395781</v>
+      </c>
+      <c r="G1729" s="2">
+        <v>1784740795551300</v>
+      </c>
+      <c r="H1729" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1729" t="s">
+        <v>187</v>
+      </c>
+      <c r="J1729" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1729" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1729" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1729">
+        <v>19</v>
+      </c>
+      <c r="R1729" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1729" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1730" s="1">
+        <v>46225.597962962966</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1730">
+        <v>2781143229</v>
+      </c>
+      <c r="G1730" s="2">
+        <v>1784740864553370</v>
+      </c>
+      <c r="H1730" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1730" t="s">
+        <v>188</v>
+      </c>
+      <c r="J1730" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1730" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1730" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1730" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1730">
+        <v>16</v>
+      </c>
+      <c r="R1730" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1730" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1731" s="1">
+        <v>46225.598171296297</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1731">
+        <v>2781143247</v>
+      </c>
+      <c r="G1731" s="2">
+        <v>1784740882553760</v>
+      </c>
+      <c r="H1731" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1731" t="s">
+        <v>188</v>
+      </c>
+      <c r="J1731" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1731" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1731" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1731" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1731">
+        <v>16</v>
+      </c>
+      <c r="R1731" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1731" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1732" s="1">
+        <v>46225.604120370372</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1732">
+        <v>2749619451</v>
+      </c>
+      <c r="G1732" s="2">
+        <v>1784741346567820</v>
+      </c>
+      <c r="H1732" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1732" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1732" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1732" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1732" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1732">
+        <v>19</v>
+      </c>
+      <c r="R1732" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1732" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1733" s="1">
+        <v>46225.605243055557</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1733">
+        <v>1809265748</v>
+      </c>
+      <c r="G1733" s="2">
+        <v>1784741489573610</v>
+      </c>
+      <c r="H1733" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1733" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1733" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1733" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1733" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1733">
+        <v>21</v>
+      </c>
+      <c r="R1733" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1733" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1734" s="1">
+        <v>46225.605381944442</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1734">
+        <v>1809265759</v>
+      </c>
+      <c r="G1734" s="2">
+        <v>1784741500574110</v>
+      </c>
+      <c r="H1734" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1734" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1734" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1734" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1734" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1734">
+        <v>19</v>
+      </c>
+      <c r="R1734" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1734" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1735" s="1">
+        <v>46225.605532407404</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1735">
+        <v>1809265770</v>
+      </c>
+      <c r="G1735" s="2">
+        <v>1784741511574520</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1735" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1735" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1735" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1735" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1735">
+        <v>19</v>
+      </c>
+      <c r="R1735" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1735" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1736" s="1">
+        <v>46225.605775462966</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1736">
+        <v>1809265791</v>
+      </c>
+      <c r="G1736" s="2">
+        <v>1784741532575220</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1736" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1736" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1736" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1736" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1736">
+        <v>21</v>
+      </c>
+      <c r="R1736" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1736" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1737" s="1">
+        <v>46225.606261574074</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1737">
+        <v>2784734947</v>
+      </c>
+      <c r="G1737" s="2">
+        <v>1784741581577810</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1737" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1737" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1737" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1737" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1737" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1737">
+        <v>16</v>
+      </c>
+      <c r="R1737" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1737" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1738" s="1">
+        <v>46225.606898148151</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1738">
+        <v>2784735002</v>
+      </c>
+      <c r="G1738" s="2">
+        <v>1784741636580030</v>
+      </c>
+      <c r="H1738" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1738" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1738" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1738" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1738" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1738">
+        <v>19</v>
+      </c>
+      <c r="R1738" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1738" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1739" s="1">
+        <v>46225.607835648145</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1739">
+        <v>2749619822</v>
+      </c>
+      <c r="G1739" s="2">
+        <v>1784741717583800</v>
+      </c>
+      <c r="H1739" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1739" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1739" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1739" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1739" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1739">
+        <v>19</v>
+      </c>
+      <c r="R1739" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1739" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1740" s="1">
+        <v>46225.608298611114</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1740">
+        <v>2749619862</v>
+      </c>
+      <c r="G1740" s="2">
+        <v>1784741757585010</v>
+      </c>
+      <c r="H1740" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1740" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1740" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1740" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1740" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1740">
+        <v>19</v>
+      </c>
+      <c r="R1740" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S1740" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1741" s="1">
+        <v>46225.609166666669</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1741">
+        <v>2748863774</v>
+      </c>
+      <c r="G1741" s="2">
+        <v>1784741832587740</v>
+      </c>
+      <c r="H1741" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1741" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1741" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1741" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1741" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1741">
+        <v>19</v>
+      </c>
+      <c r="R1741" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S1741" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1742" s="1">
+        <v>46225.6096412037</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1742">
+        <v>2748863815</v>
+      </c>
+      <c r="G1742" s="2">
+        <v>1784741873589110</v>
+      </c>
+      <c r="H1742" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1742" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1742" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1742" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1742">
+        <v>19</v>
+      </c>
+      <c r="R1742" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S1742" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1743" s="1">
+        <v>46225.611076388886</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1743">
+        <v>2772147773</v>
+      </c>
+      <c r="G1743" s="2">
+        <v>1784741997592920</v>
+      </c>
+      <c r="H1743" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1743" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1743" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1743" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1743" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1743" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1743">
+        <v>16</v>
+      </c>
+      <c r="R1743" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1743" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1744" s="1">
+        <v>46225.611620370371</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1744">
+        <v>2772147820</v>
+      </c>
+      <c r="G1744" s="2">
+        <v>1784742044594410</v>
+      </c>
+      <c r="H1744" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1744" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1744" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1744" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1744" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1744" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1744">
+        <v>16</v>
+      </c>
+      <c r="R1744" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S1744" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1745" s="1">
+        <v>46225.61273148148</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1745">
+        <v>2748857018</v>
+      </c>
+      <c r="G1745" s="2">
+        <v>1784742140598090</v>
+      </c>
+      <c r="H1745" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1745" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1745" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1745" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1745" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1745" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1745">
+        <v>16</v>
+      </c>
+      <c r="R1745" s="3">
+        <v>3.2754629629629631E-3</v>
+      </c>
+      <c r="S1745" s="3">
+        <v>3.1944444444444446E-3</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1746" s="1">
+        <v>46225.618078703701</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1746">
+        <v>2777535926</v>
+      </c>
+      <c r="G1746" s="2">
+        <v>1784742602614980</v>
+      </c>
+      <c r="H1746" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1746" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1746" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1746" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1746" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1746" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1746">
+        <v>16</v>
+      </c>
+      <c r="R1746" s="3">
+        <v>4.2824074074074075E-3</v>
+      </c>
+      <c r="S1746" s="3">
+        <v>4.0509259259259257E-3</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1747" s="1">
+        <v>46225.625578703701</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1747">
+        <v>2775180376</v>
+      </c>
+      <c r="G1747" s="2">
+        <v>1784743250638390</v>
+      </c>
+      <c r="H1747" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1747" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1747" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1747" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1747" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1747">
+        <v>19</v>
+      </c>
+      <c r="R1747" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1747" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1748" s="1">
+        <v>46225.625798611109</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1748">
+        <v>2775180395</v>
+      </c>
+      <c r="G1748" s="2">
+        <v>1784743269638700</v>
+      </c>
+      <c r="H1748" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1748" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1748" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1748" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1748" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1748">
+        <v>19</v>
+      </c>
+      <c r="R1748" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1748" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1749" s="1">
+        <v>46225.626006944447</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1749">
+        <v>1819242308</v>
+      </c>
+      <c r="G1749" s="2">
+        <v>1784743287639290</v>
+      </c>
+      <c r="H1749" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1749" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1749" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1749" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1749" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1749" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1749">
+        <v>16</v>
+      </c>
+      <c r="R1749" s="3">
+        <v>1.238425925925926E-3</v>
+      </c>
+      <c r="S1749" s="3">
+        <v>1.0879629629629629E-3</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1750" s="1">
+        <v>46225.62835648148</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1750">
+        <v>2784293467</v>
+      </c>
+      <c r="G1750" s="2">
+        <v>1784743490646320</v>
+      </c>
+      <c r="H1750" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1750" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1750" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1750" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1750" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1750" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1750">
+        <v>16</v>
+      </c>
+      <c r="R1750" s="3">
+        <v>2.8124999999999999E-3</v>
+      </c>
+      <c r="S1750" s="3">
+        <v>2.4652777777777776E-3</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1751" s="1">
+        <v>46225.639768518522</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1751">
+        <v>2783173458</v>
+      </c>
+      <c r="G1751" s="2">
+        <v>1784744476681790</v>
+      </c>
+      <c r="H1751" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1751" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1751" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1751" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1751" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1751" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1751">
+        <v>16</v>
+      </c>
+      <c r="R1751" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S1751" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1752" s="1">
+        <v>46225.640289351853</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1752">
+        <v>2783173503</v>
+      </c>
+      <c r="G1752" s="2">
+        <v>1784744521682940</v>
+      </c>
+      <c r="H1752" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1752" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1752" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1752" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1752" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1752" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1752">
+        <v>16</v>
+      </c>
+      <c r="R1752" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="S1752" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1753" s="1">
+        <v>46225.641782407409</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1753">
+        <v>2766170213</v>
+      </c>
+      <c r="G1753" s="2">
+        <v>1784744650686980</v>
+      </c>
+      <c r="H1753" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1753" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1753" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1753" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1753" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1753">
+        <v>19</v>
+      </c>
+      <c r="R1753" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1753" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1754" s="1">
+        <v>46225.642152777778</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1754">
+        <v>2766170245</v>
+      </c>
+      <c r="G1754" s="2">
+        <v>1784744682687920</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1754" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1754" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1754" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1754" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1754">
+        <v>19</v>
+      </c>
+      <c r="R1754" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1754" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1755" s="1">
+        <v>46225.643240740741</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1755">
+        <v>2783230168</v>
+      </c>
+      <c r="G1755" s="2">
+        <v>1784744776691260</v>
+      </c>
+      <c r="H1755" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1755" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1755" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1755" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1755" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1755">
+        <v>19</v>
+      </c>
+      <c r="R1755" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1755" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1756" s="1">
+        <v>46225.643368055556</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1756">
+        <v>2783230179</v>
+      </c>
+      <c r="G1756" s="2">
+        <v>1784744787691530</v>
+      </c>
+      <c r="H1756" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1756" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1756" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1756" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1756" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1756">
+        <v>19</v>
+      </c>
+      <c r="R1756" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1756" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1757" s="1">
+        <v>46225.643541666665</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1757">
+        <v>2783230194</v>
+      </c>
+      <c r="G1757" s="2">
+        <v>1784744802692030</v>
+      </c>
+      <c r="H1757" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1757" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1757" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1757" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1757" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1757">
+        <v>19</v>
+      </c>
+      <c r="R1757" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1757" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1758" s="1">
+        <v>46225.644050925926</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1758">
+        <v>2779975931</v>
+      </c>
+      <c r="G1758" s="2">
+        <v>1784744846693190</v>
+      </c>
+      <c r="H1758" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1758" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1758" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1758" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1758" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1758">
+        <v>19</v>
+      </c>
+      <c r="R1758" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S1758" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1759" s="1">
+        <v>46225.644942129627</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1759">
+        <v>2779976008</v>
+      </c>
+      <c r="G1759" s="2">
+        <v>1784744923695330</v>
+      </c>
+      <c r="H1759" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1759" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1759" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1759" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1759" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1759">
+        <v>19</v>
+      </c>
+      <c r="R1759" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1759" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1760" s="1">
+        <v>46225.645185185182</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1760">
+        <v>2779976029</v>
+      </c>
+      <c r="G1760" s="2">
+        <v>1784744944696080</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1760" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1760" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1760" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1760" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1760">
+        <v>19</v>
+      </c>
+      <c r="R1760" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1760" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1761" s="1">
+        <v>46225.646469907406</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1761">
+        <v>2759785687</v>
+      </c>
+      <c r="G1761" s="2">
+        <v>1784745055699590</v>
+      </c>
+      <c r="H1761" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1761" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1761" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1761" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1761" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1761" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1761">
+        <v>16</v>
+      </c>
+      <c r="R1761" s="3">
+        <v>8.067129629629629E-3</v>
+      </c>
+      <c r="S1761" s="3">
+        <v>7.8356481481481489E-3</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1762" s="1">
+        <v>46225.656527777777</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1762">
+        <v>2748977683</v>
+      </c>
+      <c r="G1762" s="2">
+        <v>1784745924728730</v>
+      </c>
+      <c r="H1762" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1762" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1762" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1762" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1762" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1762">
+        <v>19</v>
+      </c>
+      <c r="R1762" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1762" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1763" s="1">
+        <v>46225.657048611109</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1763">
+        <v>2748977728</v>
+      </c>
+      <c r="G1763" s="2">
+        <v>1784745969730120</v>
+      </c>
+      <c r="H1763" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1763" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1763" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1763" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1763" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1763">
+        <v>19</v>
+      </c>
+      <c r="R1763" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1763" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1764" s="1">
+        <v>46225.658368055556</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1764">
+        <v>2749229004</v>
+      </c>
+      <c r="G1764" s="2">
+        <v>1784746083732870</v>
+      </c>
+      <c r="H1764" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1764" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1764" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1764" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1764" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1764" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1764">
+        <v>16</v>
+      </c>
+      <c r="R1764" s="3">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="S1764" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1765" s="1">
+        <v>46225.659166666665</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1765">
+        <v>2749229073</v>
+      </c>
+      <c r="G1765" s="2">
+        <v>1784746152734790</v>
+      </c>
+      <c r="H1765" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1765" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1765" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1765" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1765" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1765">
+        <v>19</v>
+      </c>
+      <c r="R1765" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1765" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1766" s="1">
+        <v>46225.65934027778</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1766">
+        <v>2749229088</v>
+      </c>
+      <c r="G1766" s="2">
+        <v>1784746167735240</v>
+      </c>
+      <c r="H1766" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1766" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1766" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1766" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1766" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1766" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1766">
+        <v>16</v>
+      </c>
+      <c r="R1766" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1766" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1767" s="1">
+        <v>46225.668425925927</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1767">
+        <v>2749229873</v>
+      </c>
+      <c r="G1767" s="2">
+        <v>1784746952762380</v>
+      </c>
+      <c r="H1767" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1767" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1767" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1767" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1767" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1767">
+        <v>19</v>
+      </c>
+      <c r="R1767" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1767" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1768" s="1">
+        <v>46225.668530092589</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1768">
+        <v>2749229882</v>
+      </c>
+      <c r="G1768" s="2">
+        <v>1784746961762740</v>
+      </c>
+      <c r="H1768" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1768" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1768" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1768" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1768" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1768">
+        <v>19</v>
+      </c>
+      <c r="R1768" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1768" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1769" s="1">
+        <v>46225.669317129628</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1769">
+        <v>2783816781</v>
+      </c>
+      <c r="G1769" s="2">
+        <v>1784747029764780</v>
+      </c>
+      <c r="H1769" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1769" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1769" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1769" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1769" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1769" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1769">
+        <v>16</v>
+      </c>
+      <c r="R1769" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="S1769" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1770" s="1">
+        <v>46225.670624999999</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1770">
+        <v>2758307125</v>
+      </c>
+      <c r="G1770" s="2">
+        <v>1784747142767630</v>
+      </c>
+      <c r="H1770" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1770" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1770" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1770" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1770" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1770" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1770">
+        <v>16</v>
+      </c>
+      <c r="R1770" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S1770" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1771" s="1">
+        <v>46225.670960648145</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1771">
+        <v>2758307154</v>
+      </c>
+      <c r="G1771" s="2">
+        <v>1784747171768720</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1771" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1771" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1771" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1771" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1771">
+        <v>19</v>
+      </c>
+      <c r="R1771" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1771" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1772" s="1">
+        <v>46225.671296296299</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1772">
+        <v>2782020308</v>
+      </c>
+      <c r="G1772" s="2">
+        <v>1784747200769940</v>
+      </c>
+      <c r="H1772" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1772" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1772" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1772" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1772" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1772">
+        <v>19</v>
+      </c>
+      <c r="R1772" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1772" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1773" s="1">
+        <v>46225.671435185184</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1773">
+        <v>2782020321</v>
+      </c>
+      <c r="G1773" s="2">
+        <v>1784747212770350</v>
+      </c>
+      <c r="H1773" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1773" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1773" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1773" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1773" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1773">
+        <v>19</v>
+      </c>
+      <c r="R1773" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1773" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1774" s="1">
+        <v>46225.672361111108</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1774">
+        <v>2777539120</v>
+      </c>
+      <c r="G1774" s="2">
+        <v>1784747292772990</v>
+      </c>
+      <c r="H1774" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1774" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1774" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1774" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1774" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1774">
+        <v>19</v>
+      </c>
+      <c r="R1774" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1774" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1775" s="1">
+        <v>46225.672615740739</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1775">
+        <v>2777539142</v>
+      </c>
+      <c r="G1775" s="2">
+        <v>1784747314773590</v>
+      </c>
+      <c r="H1775" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1775" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1775" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1775" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1775" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1775">
+        <v>19</v>
+      </c>
+      <c r="R1775" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1775" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1776" s="1">
+        <v>46225.673217592594</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1776">
+        <v>2748860389</v>
+      </c>
+      <c r="G1776" s="2">
+        <v>1784747366775290</v>
+      </c>
+      <c r="H1776" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1776" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1776" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1776" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1776" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1776">
+        <v>19</v>
+      </c>
+      <c r="R1776" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1776" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1777" s="1">
+        <v>46225.673437500001</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1777">
+        <v>2748860408</v>
+      </c>
+      <c r="G1777" s="2">
+        <v>1784747385775770</v>
+      </c>
+      <c r="H1777" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1777" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1777" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1777" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1777" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1777" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1777">
+        <v>16</v>
+      </c>
+      <c r="R1777" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1777" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1778" s="1">
+        <v>46225.674247685187</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1778">
+        <v>2749339526</v>
+      </c>
+      <c r="G1778" s="2">
+        <v>1784747455778390</v>
+      </c>
+      <c r="H1778" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1778" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1778" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1778" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1778" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1778">
+        <v>19</v>
+      </c>
+      <c r="R1778" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1778" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1779" s="1">
+        <v>46225.674456018518</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1779">
+        <v>2749339544</v>
+      </c>
+      <c r="G1779" s="2">
+        <v>1784747473779130</v>
+      </c>
+      <c r="H1779" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1779" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1779" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1779" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1779" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1779" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1779">
+        <v>16</v>
+      </c>
+      <c r="R1779" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1779" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1780" s="1">
+        <v>46225.674803240741</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1780">
+        <v>2749339574</v>
+      </c>
+      <c r="G1780" s="2">
+        <v>1784747503780670</v>
+      </c>
+      <c r="H1780" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1780" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1780" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1780" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1780" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1780">
+        <v>19</v>
+      </c>
+      <c r="R1780" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1780" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1781" s="1">
+        <v>46225.675462962965</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1781">
+        <v>2749339631</v>
+      </c>
+      <c r="G1781" s="2">
+        <v>1784747560782890</v>
+      </c>
+      <c r="H1781" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1781" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1781" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1781" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1781" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1781">
+        <v>19</v>
+      </c>
+      <c r="R1781" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1781" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1782" s="1">
+        <v>46225.67690972222</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1782">
+        <v>2749339756</v>
+      </c>
+      <c r="G1782" s="2">
+        <v>1784747685787720</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1782" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1782" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1782" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1782" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1782">
+        <v>19</v>
+      </c>
+      <c r="R1782" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1782" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1783" s="1">
+        <v>46225.678136574075</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1783">
+        <v>2784192163</v>
+      </c>
+      <c r="G1783" s="2">
+        <v>1784747791791080</v>
+      </c>
+      <c r="H1783" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1783" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1783" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1783" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1783" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1783" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1783">
+        <v>16</v>
+      </c>
+      <c r="R1783" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1783" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1784" s="1">
+        <v>46225.678449074076</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1784">
+        <v>2784192190</v>
+      </c>
+      <c r="G1784" s="2">
+        <v>1784747818792230</v>
+      </c>
+      <c r="H1784" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1784" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1784" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1784" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1784" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1784" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1784">
+        <v>16</v>
+      </c>
+      <c r="R1784" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1784" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1785" s="1">
+        <v>46225.67900462963</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1785">
+        <v>2777520792</v>
+      </c>
+      <c r="G1785" s="2">
+        <v>1784747866793650</v>
+      </c>
+      <c r="H1785" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1785" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1785" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1785" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1785" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1785" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1785">
+        <v>16</v>
+      </c>
+      <c r="R1785" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1785" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1786" s="1">
+        <v>46225.679189814815</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1786">
+        <v>2777520808</v>
+      </c>
+      <c r="G1786" s="2">
+        <v>1784747882794290</v>
+      </c>
+      <c r="H1786" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1786" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1786" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1786" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1786" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1786" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1786">
+        <v>16</v>
+      </c>
+      <c r="R1786" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1786" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1787" s="1">
+        <v>46225.679606481484</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1787">
+        <v>2764733929</v>
+      </c>
+      <c r="G1787" s="2">
+        <v>1784747918795500</v>
+      </c>
+      <c r="H1787" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1787" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1787" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1787" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1787" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1787">
+        <v>19</v>
+      </c>
+      <c r="R1787" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1787" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1788" s="1">
+        <v>46225.679791666669</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1788">
+        <v>2764733945</v>
+      </c>
+      <c r="G1788" s="2">
+        <v>1784747934796120</v>
+      </c>
+      <c r="H1788" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1788" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1788" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1788" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1788" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1788">
+        <v>19</v>
+      </c>
+      <c r="R1788" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1788" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1789" s="1">
+        <v>46225.679918981485</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1789">
+        <v>2764733956</v>
+      </c>
+      <c r="G1789" s="2">
+        <v>1784747945796550</v>
+      </c>
+      <c r="H1789" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1789" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1789" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1789" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1789" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1789">
+        <v>19</v>
+      </c>
+      <c r="R1789" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1789" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1790" s="1">
+        <v>46225.680138888885</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1790">
+        <v>2764733975</v>
+      </c>
+      <c r="G1790" s="2">
+        <v>1784747964797190</v>
+      </c>
+      <c r="H1790" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1790" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1790" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1790" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1790" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1790">
+        <v>19</v>
+      </c>
+      <c r="R1790" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1790" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1791" s="1">
+        <v>46225.681168981479</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1791">
+        <v>2778611255</v>
+      </c>
+      <c r="G1791" s="2">
+        <v>1784748053800580</v>
+      </c>
+      <c r="H1791" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1791" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1791" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1791" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1791" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1791">
+        <v>19</v>
+      </c>
+      <c r="R1791" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1791" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1792" s="1">
+        <v>46225.681539351855</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1792">
+        <v>2778611287</v>
+      </c>
+      <c r="G1792" s="2">
+        <v>1784748085801670</v>
+      </c>
+      <c r="H1792" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1792" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1792" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1792" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1792" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1792" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1792">
+        <v>16</v>
+      </c>
+      <c r="R1792" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S1792" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1793" s="1">
+        <v>46225.682210648149</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1793">
+        <v>2782325574</v>
+      </c>
+      <c r="G1793" s="2">
+        <v>1784748143803780</v>
+      </c>
+      <c r="H1793" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1793" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1793" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1793" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1793" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1793">
+        <v>19</v>
+      </c>
+      <c r="R1793" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1793" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1794" s="1">
+        <v>46225.682453703703</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1794">
+        <v>2782325595</v>
+      </c>
+      <c r="G1794" s="2">
+        <v>1784748164804270</v>
+      </c>
+      <c r="H1794" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1794" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1794" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1794" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1794" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1794">
+        <v>19</v>
+      </c>
+      <c r="R1794" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1794" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1795" s="1">
+        <v>46225.68372685185</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1795">
+        <v>2772648485</v>
+      </c>
+      <c r="G1795" s="2">
+        <v>1784748274807720</v>
+      </c>
+      <c r="H1795" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1795" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1795" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1795" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1795" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1795">
+        <v>19</v>
+      </c>
+      <c r="R1795" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1795" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1796" s="1">
+        <v>46225.68478009259</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1796" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1796">
+        <v>2772648526</v>
+      </c>
+      <c r="G1796" s="2">
+        <v>1784748315808800</v>
+      </c>
+      <c r="H1796" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1796" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1796" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1796" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1796" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1796">
+        <v>19</v>
+      </c>
+      <c r="R1796" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1796" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1797" s="1">
+        <v>46225.68550925926</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1797" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1797">
+        <v>2784359355</v>
+      </c>
+      <c r="G1797" s="2">
+        <v>1784748428812470</v>
+      </c>
+      <c r="H1797" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1797" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1797" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1797" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1797" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1797" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1797">
+        <v>16</v>
+      </c>
+      <c r="R1797" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1797" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1798" s="1">
+        <v>46225.685833333337</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1798" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1798">
+        <v>2784359384</v>
+      </c>
+      <c r="G1798" s="2">
+        <v>1784748456813330</v>
+      </c>
+      <c r="H1798" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1798" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1798" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1798" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1798" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1798" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1798">
+        <v>16</v>
+      </c>
+      <c r="R1798" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1798" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1799" s="1">
+        <v>46225.68644675926</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1799" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1799">
+        <v>2783010702</v>
+      </c>
+      <c r="G1799" s="2">
+        <v>1784748509814820</v>
+      </c>
+      <c r="H1799" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1799" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1799" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1799" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1799" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1799" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1799">
+        <v>16</v>
+      </c>
+      <c r="R1799" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1799" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1800" s="1">
+        <v>46225.686689814815</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1800" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1800">
+        <v>2783010723</v>
+      </c>
+      <c r="G1800" s="2">
+        <v>1784748530815840</v>
+      </c>
+      <c r="H1800" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1800" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1800" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1800" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1800" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1800" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1800">
+        <v>16</v>
+      </c>
+      <c r="R1800" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1800" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1801" s="1">
+        <v>46225.6874537037</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1801" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1801">
+        <v>2782355703</v>
+      </c>
+      <c r="G1801" s="2">
+        <v>1784748596818150</v>
+      </c>
+      <c r="H1801" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1801" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1801" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1801" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1801" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1801" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1801">
+        <v>16</v>
+      </c>
+      <c r="R1801" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="S1801" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1802" s="1">
+        <v>46225.689236111109</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1802" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1802">
+        <v>2782903235</v>
+      </c>
+      <c r="G1802" s="2">
+        <v>1784748700821750</v>
+      </c>
+      <c r="H1802" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1802" t="s">
+        <v>170</v>
+      </c>
+      <c r="J1802" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1802" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1802" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1802">
+        <v>19</v>
+      </c>
+      <c r="R1802" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1802" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1803" s="1">
+        <v>46225.690162037034</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1803" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1803">
+        <v>2784706942</v>
+      </c>
+      <c r="G1803" s="2">
+        <v>1784748830825630</v>
+      </c>
+      <c r="H1803" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1803" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1803" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1803" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1803" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1803" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1803">
+        <v>16</v>
+      </c>
+      <c r="R1803" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1803" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1804" s="1">
+        <v>46225.690486111111</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1804" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1804">
+        <v>2784706970</v>
+      </c>
+      <c r="G1804" s="2">
+        <v>1784748858826390</v>
+      </c>
+      <c r="H1804" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1804" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1804" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1804" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1804" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1804">
+        <v>19</v>
+      </c>
+      <c r="R1804" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1804" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1805" s="1">
+        <v>46225.691145833334</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1805" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1805">
+        <v>2784172887</v>
+      </c>
+      <c r="G1805" s="2">
+        <v>1784748915827840</v>
+      </c>
+      <c r="H1805" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1805" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1805" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1805" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1805" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1805" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1805">
+        <v>16</v>
+      </c>
+      <c r="R1805" s="3">
+        <v>4.5370370370370373E-3</v>
+      </c>
+      <c r="S1805" s="3">
+        <v>4.3518518518518515E-3</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1806" s="1">
+        <v>46225.696828703702</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1806" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1806">
+        <v>2783846514</v>
+      </c>
+      <c r="G1806" s="2">
+        <v>1784749406840780</v>
+      </c>
+      <c r="H1806" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1806" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1806" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1806" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1806" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1806" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1806">
+        <v>16</v>
+      </c>
+      <c r="R1806" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S1806" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1807" s="1">
+        <v>46225.698252314818</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1807" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1807">
+        <v>2784572688</v>
+      </c>
+      <c r="G1807" s="2">
+        <v>1784749529844010</v>
+      </c>
+      <c r="H1807" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1807" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1807" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1807" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1807" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1807" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1807">
+        <v>16</v>
+      </c>
+      <c r="R1807" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1807" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1808" s="1">
+        <v>46225.699664351851</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1808" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1808">
+        <v>2749274379</v>
+      </c>
+      <c r="G1808" s="2">
+        <v>1784749651847200</v>
+      </c>
+      <c r="H1808" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1808" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1808" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1808" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1808" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1808" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1808">
+        <v>16</v>
+      </c>
+      <c r="R1808" s="3">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="S1808" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1809" s="1">
+        <v>46225.707592592589</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1809" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1809">
+        <v>2784103505</v>
+      </c>
+      <c r="G1809" s="2">
+        <v>1784750336870720</v>
+      </c>
+      <c r="H1809" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1809" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1809" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1809" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1809" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1809" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1809">
+        <v>16</v>
+      </c>
+      <c r="R1809" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="S1809" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1810" s="1">
+        <v>46225.708368055559</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1810" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1810">
+        <v>2784103572</v>
+      </c>
+      <c r="G1810" s="2">
+        <v>1784750403872960</v>
+      </c>
+      <c r="H1810" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1810" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1810" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1810" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1810" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1810">
+        <v>19</v>
+      </c>
+      <c r="R1810" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1810" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1811" s="1">
+        <v>46225.708912037036</v>
+      </c>
+      <c r="B1811" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1811" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1811">
+        <v>2755981260</v>
+      </c>
+      <c r="G1811" s="2">
+        <v>1784750450874990</v>
+      </c>
+      <c r="H1811" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1811" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1811" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1811" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1811" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1811">
+        <v>19</v>
+      </c>
+      <c r="R1811" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1811" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1812" s="1">
+        <v>46225.709502314814</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1812" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1812">
+        <v>2755981311</v>
+      </c>
+      <c r="G1812" s="2">
+        <v>1784750501877050</v>
+      </c>
+      <c r="H1812" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1812" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1812" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1812" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1812" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1812">
+        <v>19</v>
+      </c>
+      <c r="R1812" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S1812" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1813" s="1">
+        <v>46225.711493055554</v>
+      </c>
+      <c r="B1813" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1813" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1813">
+        <v>2777262978</v>
+      </c>
+      <c r="G1813" s="2">
+        <v>1784750673883630</v>
+      </c>
+      <c r="H1813" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1813" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1813" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1813" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1813" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1813">
+        <v>19</v>
+      </c>
+      <c r="R1813" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S1813" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1814" s="1">
+        <v>46225.712071759262</v>
+      </c>
+      <c r="B1814" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1814" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1814">
+        <v>2777263028</v>
+      </c>
+      <c r="G1814" s="2">
+        <v>1784750723885520</v>
+      </c>
+      <c r="H1814" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1814" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1814" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1814" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1814" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1814" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1814">
+        <v>16</v>
+      </c>
+      <c r="R1814" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="S1814" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1815" s="1">
+        <v>46225.713449074072</v>
+      </c>
+      <c r="B1815" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1815" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1815">
+        <v>2777723044</v>
+      </c>
+      <c r="G1815" s="2">
+        <v>1784750842889670</v>
+      </c>
+      <c r="H1815" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1815" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1815" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1815" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1815" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1815" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1815">
+        <v>16</v>
+      </c>
+      <c r="R1815" s="3">
+        <v>4.8726851851851848E-3</v>
+      </c>
+      <c r="S1815" s="3">
+        <v>4.7106481481481478E-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Discagem_Smart Factory Agendamentos.xlsx
+++ b/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Discagem_Smart Factory Agendamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Agendamento_Smart_Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EF9EF3-69B8-4E9B-80DE-D8A98903C5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334174D3-A610-4240-AD2B-5C3CD3BFB989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{18287E13-523A-4B69-86E2-0C7AA7A14E38}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{18287E13-523A-4B69-86E2-0C7AA7A14E38}"/>
   </bookViews>
   <sheets>
     <sheet name="chamadas_10-07-2026_124916" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14541" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16079" uniqueCount="190">
   <si>
     <t>DATA</t>
   </si>
@@ -587,6 +587,9 @@
   </si>
   <si>
     <t>(21) 99640-2344</t>
+  </si>
+  <si>
+    <t>(22) 99741-1291</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCA3C27-62A6-41B6-A964-C148E02992FA}">
-  <dimension ref="A1:S1815"/>
+  <dimension ref="A1:S2007"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -77070,6 +77073,8097 @@
         <v>4.7106481481481478E-3</v>
       </c>
     </row>
+    <row r="1816" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1816" s="1">
+        <v>46226.382638888892</v>
+      </c>
+      <c r="B1816" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1816" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1816">
+        <v>2784802026</v>
+      </c>
+      <c r="G1816" s="2">
+        <v>178480866082271</v>
+      </c>
+      <c r="H1816" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1816" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1816" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1816" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1816" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1816">
+        <v>19</v>
+      </c>
+      <c r="R1816" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1816" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1817" s="1">
+        <v>46226.382777777777</v>
+      </c>
+      <c r="B1817" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1817" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1817">
+        <v>2784802038</v>
+      </c>
+      <c r="G1817" s="2">
+        <v>178480867282481</v>
+      </c>
+      <c r="H1817" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1817" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1817" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1817" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1817" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1817">
+        <v>19</v>
+      </c>
+      <c r="R1817" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1817" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1818" s="1">
+        <v>46226.383587962962</v>
+      </c>
+      <c r="B1818" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1818" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1818">
+        <v>1809332995</v>
+      </c>
+      <c r="G1818" s="2">
+        <v>178480873684101</v>
+      </c>
+      <c r="H1818" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1818" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1818" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1818" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1818" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1818">
+        <v>21</v>
+      </c>
+      <c r="R1818" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1818" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1819" s="1">
+        <v>46226.383761574078</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1819" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1819">
+        <v>1809333009</v>
+      </c>
+      <c r="G1819" s="2">
+        <v>178480874984591</v>
+      </c>
+      <c r="H1819" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1819" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1819" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1819" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1819" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1819">
+        <v>19</v>
+      </c>
+      <c r="R1819" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1819" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1820" s="1">
+        <v>46226.383935185186</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1820" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1820">
+        <v>1809333025</v>
+      </c>
+      <c r="G1820" s="2">
+        <v>178480876685061</v>
+      </c>
+      <c r="H1820" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1820" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1820" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1820" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1820" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1820">
+        <v>19</v>
+      </c>
+      <c r="R1820" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1820" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1821" s="1">
+        <v>46226.384062500001</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1821" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1821">
+        <v>1809333038</v>
+      </c>
+      <c r="G1821" s="2">
+        <v>178480877985561</v>
+      </c>
+      <c r="H1821" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1821" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1821" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1821" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1821" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1821">
+        <v>21</v>
+      </c>
+      <c r="R1821" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1821" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1822" s="1">
+        <v>46226.384236111109</v>
+      </c>
+      <c r="B1822" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1822" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1822">
+        <v>1809333050</v>
+      </c>
+      <c r="G1822" s="2">
+        <v>178480879185901</v>
+      </c>
+      <c r="H1822" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1822" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1822" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1822" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1822" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1822">
+        <v>19</v>
+      </c>
+      <c r="R1822" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1822" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1823" s="1">
+        <v>46226.384363425925</v>
+      </c>
+      <c r="B1823" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1823" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1823">
+        <v>1809333064</v>
+      </c>
+      <c r="G1823" s="2">
+        <v>178480880586281</v>
+      </c>
+      <c r="H1823" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1823" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1823" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1823" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1823" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1823">
+        <v>19</v>
+      </c>
+      <c r="R1823" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1823" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1824" s="1">
+        <v>46226.384629629632</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1824" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1824">
+        <v>1809333084</v>
+      </c>
+      <c r="G1824" s="2">
+        <v>178480882586881</v>
+      </c>
+      <c r="H1824" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1824" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1824" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1824" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1824" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1824">
+        <v>21</v>
+      </c>
+      <c r="R1824" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1824" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1825" s="1">
+        <v>46226.38490740741</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1825" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1825">
+        <v>2768877020</v>
+      </c>
+      <c r="G1825" s="2">
+        <v>178480885688081</v>
+      </c>
+      <c r="H1825" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1825" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1825" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1825" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1825" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1825" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1825">
+        <v>16</v>
+      </c>
+      <c r="R1825" s="3">
+        <v>9.2592592592592587E-3</v>
+      </c>
+      <c r="S1825" s="3">
+        <v>9.1550925925925931E-3</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1826" s="1">
+        <v>46226.403749999998</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1826" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1826">
+        <v>2777782687</v>
+      </c>
+      <c r="G1826" s="2">
+        <v>1784810484136840</v>
+      </c>
+      <c r="H1826" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1826" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1826" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1826" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1826" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1826" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1826">
+        <v>16</v>
+      </c>
+      <c r="R1826" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="S1826" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1827" s="1">
+        <v>46226.404652777775</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1827" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1827">
+        <v>2777782764</v>
+      </c>
+      <c r="G1827" s="2">
+        <v>1784810562139220</v>
+      </c>
+      <c r="H1827" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1827" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1827" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1827" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1827" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1827" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1827">
+        <v>16</v>
+      </c>
+      <c r="R1827" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1827" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1828" s="1">
+        <v>46226.404976851853</v>
+      </c>
+      <c r="B1828" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1828" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1828">
+        <v>2777782792</v>
+      </c>
+      <c r="G1828" s="2">
+        <v>1784810590140230</v>
+      </c>
+      <c r="H1828" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1828" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1828" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1828" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1828" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1828">
+        <v>19</v>
+      </c>
+      <c r="R1828" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1828" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1829" s="1">
+        <v>46226.405092592591</v>
+      </c>
+      <c r="B1829" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1829" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1829">
+        <v>2777782802</v>
+      </c>
+      <c r="G1829" s="2">
+        <v>1784810600140690</v>
+      </c>
+      <c r="H1829" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1829" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1829" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1829" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1829" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1829">
+        <v>19</v>
+      </c>
+      <c r="R1829" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1829" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1830" s="1">
+        <v>46226.405775462961</v>
+      </c>
+      <c r="B1830" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1830" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1830">
+        <v>2773058522</v>
+      </c>
+      <c r="G1830" s="2">
+        <v>1784810659142550</v>
+      </c>
+      <c r="H1830" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1830" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1830" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1830" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1830" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1830">
+        <v>19</v>
+      </c>
+      <c r="R1830" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1830" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1831" s="1">
+        <v>46226.406087962961</v>
+      </c>
+      <c r="B1831" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1831" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1831">
+        <v>2773058549</v>
+      </c>
+      <c r="G1831" s="2">
+        <v>1784810686143320</v>
+      </c>
+      <c r="H1831" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1831" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1831" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1831" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1831" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1831" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1831">
+        <v>16</v>
+      </c>
+      <c r="R1831" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1831" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1832" s="1">
+        <v>46226.406527777777</v>
+      </c>
+      <c r="B1832" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1832" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1832">
+        <v>2773058587</v>
+      </c>
+      <c r="G1832" s="2">
+        <v>1784810724144560</v>
+      </c>
+      <c r="H1832" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1832" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1832" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1832" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1832" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1832" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1832">
+        <v>16</v>
+      </c>
+      <c r="R1832" s="3">
+        <v>1.3657407407407407E-3</v>
+      </c>
+      <c r="S1832" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1833" s="1">
+        <v>46226.412037037036</v>
+      </c>
+      <c r="B1833" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1833" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1833">
+        <v>2784428336</v>
+      </c>
+      <c r="G1833" s="2">
+        <v>1784811200156580</v>
+      </c>
+      <c r="H1833" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1833" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1833" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1833" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1833" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1833" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1833">
+        <v>16</v>
+      </c>
+      <c r="R1833" s="3">
+        <v>5.5902777777777773E-3</v>
+      </c>
+      <c r="S1833" s="3">
+        <v>5.4513888888888893E-3</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1834" s="1">
+        <v>46226.435532407406</v>
+      </c>
+      <c r="B1834" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1834" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1834">
+        <v>2765953988</v>
+      </c>
+      <c r="G1834" s="2">
+        <v>1784813230214710</v>
+      </c>
+      <c r="H1834" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1834" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1834" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1834" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1834" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1834" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1834">
+        <v>16</v>
+      </c>
+      <c r="R1834" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1834" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1835" s="1">
+        <v>46226.435694444444</v>
+      </c>
+      <c r="B1835" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1835" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1835">
+        <v>2765954002</v>
+      </c>
+      <c r="G1835" s="2">
+        <v>1784813244215070</v>
+      </c>
+      <c r="H1835" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1835" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1835" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1835" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1835" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1835" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1835">
+        <v>16</v>
+      </c>
+      <c r="R1835" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1835" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1836" s="1">
+        <v>46226.435856481483</v>
+      </c>
+      <c r="B1836" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1836" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1836">
+        <v>2765954016</v>
+      </c>
+      <c r="G1836" s="2">
+        <v>1784813258215510</v>
+      </c>
+      <c r="H1836" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1836" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1836" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1836" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1836" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1836" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1836">
+        <v>16</v>
+      </c>
+      <c r="R1836" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1836" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1837" s="1">
+        <v>46226.436655092592</v>
+      </c>
+      <c r="B1837" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1837" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1837">
+        <v>2764713659</v>
+      </c>
+      <c r="G1837" s="2">
+        <v>1784813327217180</v>
+      </c>
+      <c r="H1837" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1837" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1837" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1837" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1837" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1837" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1837">
+        <v>16</v>
+      </c>
+      <c r="R1837" s="3">
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="S1837" s="3">
+        <v>7.3842592592592597E-3</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1838" s="1">
+        <v>46226.468680555554</v>
+      </c>
+      <c r="B1838" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1838" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1838">
+        <v>2777694566</v>
+      </c>
+      <c r="G1838" s="2">
+        <v>1784816094307240</v>
+      </c>
+      <c r="H1838" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1838" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1838" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1838" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1838" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1838" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1838">
+        <v>16</v>
+      </c>
+      <c r="R1838" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="S1838" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1839" s="1">
+        <v>46226.46947916667</v>
+      </c>
+      <c r="B1839" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1839" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1839">
+        <v>2777694635</v>
+      </c>
+      <c r="G1839" s="2">
+        <v>1784816163309000</v>
+      </c>
+      <c r="H1839" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1839" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1839" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1839" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1839" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1839">
+        <v>19</v>
+      </c>
+      <c r="R1839" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1839" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1840" s="1">
+        <v>46226.470891203702</v>
+      </c>
+      <c r="B1840" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1840" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1840">
+        <v>2778334623</v>
+      </c>
+      <c r="G1840" s="2">
+        <v>1784816285312490</v>
+      </c>
+      <c r="H1840" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1840" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1840" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1840" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1840" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1840">
+        <v>19</v>
+      </c>
+      <c r="R1840" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1840" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1841" s="1">
+        <v>46226.471238425926</v>
+      </c>
+      <c r="B1841" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1841" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1841">
+        <v>2778334653</v>
+      </c>
+      <c r="G1841" s="2">
+        <v>1784816315313530</v>
+      </c>
+      <c r="H1841" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1841" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1841" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1841" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1841" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1841" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1841">
+        <v>16</v>
+      </c>
+      <c r="R1841" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1841" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1842" s="1">
+        <v>46226.473495370374</v>
+      </c>
+      <c r="B1842" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1842" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1842">
+        <v>2777055515</v>
+      </c>
+      <c r="G1842" s="2">
+        <v>1784816510317940</v>
+      </c>
+      <c r="H1842" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1842" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1842" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1842" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1842" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1842">
+        <v>19</v>
+      </c>
+      <c r="R1842" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1842" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1843" s="1">
+        <v>46226.473680555559</v>
+      </c>
+      <c r="B1843" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1843" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1843">
+        <v>2777055531</v>
+      </c>
+      <c r="G1843" s="2">
+        <v>1784816526318220</v>
+      </c>
+      <c r="H1843" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1843" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1843" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1843" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1843" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1843">
+        <v>19</v>
+      </c>
+      <c r="R1843" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1843" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1844" s="1">
+        <v>46226.477546296293</v>
+      </c>
+      <c r="B1844" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1844" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1844">
+        <v>2777055865</v>
+      </c>
+      <c r="G1844" s="2">
+        <v>1784816860325970</v>
+      </c>
+      <c r="H1844" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1844" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1844" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1844" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1844" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1844">
+        <v>19</v>
+      </c>
+      <c r="R1844" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1844" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1845" s="1">
+        <v>46226.478067129632</v>
+      </c>
+      <c r="B1845" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1845" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1845">
+        <v>2773298734</v>
+      </c>
+      <c r="G1845" s="2">
+        <v>1784816905326600</v>
+      </c>
+      <c r="H1845" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1845" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1845" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1845" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1845" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1845" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1845">
+        <v>16</v>
+      </c>
+      <c r="R1845" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S1845" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1846" s="1">
+        <v>46226.478692129633</v>
+      </c>
+      <c r="B1846" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1846" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1846">
+        <v>2773298788</v>
+      </c>
+      <c r="G1846" s="2">
+        <v>1784816959327440</v>
+      </c>
+      <c r="H1846" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1846" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1846" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1846" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1846" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1846" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1846">
+        <v>16</v>
+      </c>
+      <c r="R1846" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S1846" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1847" s="1">
+        <v>46226.479502314818</v>
+      </c>
+      <c r="B1847" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1847" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1847">
+        <v>2772228252</v>
+      </c>
+      <c r="G1847" s="2">
+        <v>1784817029328530</v>
+      </c>
+      <c r="H1847" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1847" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1847" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1847" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1847" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1847">
+        <v>19</v>
+      </c>
+      <c r="R1847" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1847" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1848" s="1">
+        <v>46226.479942129627</v>
+      </c>
+      <c r="B1848" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1848" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1848">
+        <v>2772228290</v>
+      </c>
+      <c r="G1848" s="2">
+        <v>1784817067329290</v>
+      </c>
+      <c r="H1848" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1848" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1848" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1848" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1848" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1848">
+        <v>19</v>
+      </c>
+      <c r="R1848" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1848" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1849" s="1">
+        <v>46226.481111111112</v>
+      </c>
+      <c r="B1849" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1849" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1849">
+        <v>2782228470</v>
+      </c>
+      <c r="G1849" s="2">
+        <v>1784817157330830</v>
+      </c>
+      <c r="H1849" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1849" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1849" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1849" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1849" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1849">
+        <v>34</v>
+      </c>
+      <c r="R1849" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1849" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1850" s="1">
+        <v>46226.481307870374</v>
+      </c>
+      <c r="B1850" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1850" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1850">
+        <v>2782228488</v>
+      </c>
+      <c r="G1850" s="2">
+        <v>1784817175331060</v>
+      </c>
+      <c r="H1850" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1850" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1850" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1850" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1850" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1850">
+        <v>21</v>
+      </c>
+      <c r="R1850" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1850" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1851" s="1">
+        <v>46226.48233796296</v>
+      </c>
+      <c r="B1851" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1851" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1851">
+        <v>2756877548</v>
+      </c>
+      <c r="G1851" s="2">
+        <v>1784817214332100</v>
+      </c>
+      <c r="H1851" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1851" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1851" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1851" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1851" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1851">
+        <v>19</v>
+      </c>
+      <c r="R1851" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1851" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1852" s="1">
+        <v>46226.482442129629</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1852" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1852">
+        <v>2756877617</v>
+      </c>
+      <c r="G1852" s="2">
+        <v>1784817283333680</v>
+      </c>
+      <c r="H1852" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1852" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1852" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1852" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1852" t="s">
+        <v>115</v>
+      </c>
+      <c r="N1852" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1852">
+        <v>16</v>
+      </c>
+      <c r="R1852" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1852" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1853" s="1">
+        <v>46226.485127314816</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1853" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1853">
+        <v>2784810881</v>
+      </c>
+      <c r="G1853" s="2">
+        <v>1784817515338260</v>
+      </c>
+      <c r="H1853" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1853" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1853" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1853" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1853" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1853">
+        <v>19</v>
+      </c>
+      <c r="R1853" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1853" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1854" s="1">
+        <v>46226.485497685186</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1854" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1854">
+        <v>2784810913</v>
+      </c>
+      <c r="G1854" s="2">
+        <v>1784817547338820</v>
+      </c>
+      <c r="H1854" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1854" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1854" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1854" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1854" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1854">
+        <v>19</v>
+      </c>
+      <c r="R1854" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1854" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1855" s="1">
+        <v>46226.486006944448</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1855" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1855">
+        <v>1809341845</v>
+      </c>
+      <c r="G1855" s="2">
+        <v>1784817586339290</v>
+      </c>
+      <c r="H1855" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1855" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1855" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1855" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1855" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1855">
+        <v>19</v>
+      </c>
+      <c r="R1855" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1855" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1856" s="1">
+        <v>46226.486168981479</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1856" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1856">
+        <v>1809341857</v>
+      </c>
+      <c r="G1856" s="2">
+        <v>1784817598339540</v>
+      </c>
+      <c r="H1856" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1856" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1856" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1856" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1856" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1856">
+        <v>19</v>
+      </c>
+      <c r="R1856" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1856" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1857" s="1">
+        <v>46226.486342592594</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1857" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1857">
+        <v>1809341871</v>
+      </c>
+      <c r="G1857" s="2">
+        <v>1784817611339840</v>
+      </c>
+      <c r="H1857" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1857" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1857" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1857" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1857" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1857">
+        <v>21</v>
+      </c>
+      <c r="R1857" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1857" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1858" s="1">
+        <v>46226.486446759256</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1858" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1858">
+        <v>1809341887</v>
+      </c>
+      <c r="G1858" s="2">
+        <v>1784817628340120</v>
+      </c>
+      <c r="H1858" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1858" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1858" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1858" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1858" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1858">
+        <v>19</v>
+      </c>
+      <c r="R1858" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1858" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1859" s="1">
+        <v>46226.486701388887</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1859" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1859">
+        <v>1809341909</v>
+      </c>
+      <c r="G1859" s="2">
+        <v>1784817650340550</v>
+      </c>
+      <c r="H1859" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1859" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1859" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1859" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1859" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1859">
+        <v>19</v>
+      </c>
+      <c r="R1859" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1859" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1860" s="1">
+        <v>46226.487025462964</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1860" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1860">
+        <v>2784811045</v>
+      </c>
+      <c r="G1860" s="2">
+        <v>1784817679341430</v>
+      </c>
+      <c r="H1860" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1860" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1860" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1860" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1860" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1860" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1860">
+        <v>16</v>
+      </c>
+      <c r="R1860" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1860" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1861" s="1">
+        <v>46226.487534722219</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1861" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1861">
+        <v>2784811089</v>
+      </c>
+      <c r="G1861" s="2">
+        <v>1784817723342510</v>
+      </c>
+      <c r="H1861" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1861" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1861" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1861" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1861" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1861" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1861">
+        <v>16</v>
+      </c>
+      <c r="R1861" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1861" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1862" s="1">
+        <v>46226.488506944443</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1862" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1862">
+        <v>2784811173</v>
+      </c>
+      <c r="G1862" s="2">
+        <v>1784817807345250</v>
+      </c>
+      <c r="H1862" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1862" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1862" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1862" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1862" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1862">
+        <v>19</v>
+      </c>
+      <c r="R1862" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1862" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1863" s="1">
+        <v>46226.48951388889</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1863" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1863">
+        <v>2749695950</v>
+      </c>
+      <c r="G1863" s="2">
+        <v>1784817845346450</v>
+      </c>
+      <c r="H1863" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1863" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1863" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1863" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1863" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1863">
+        <v>19</v>
+      </c>
+      <c r="R1863" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1863" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1864" s="1">
+        <v>46226.489594907405</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1864" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1864">
+        <v>2749696006</v>
+      </c>
+      <c r="G1864" s="2">
+        <v>1784817901348790</v>
+      </c>
+      <c r="H1864" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1864" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1864" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1864" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1864" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1864" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1864">
+        <v>16</v>
+      </c>
+      <c r="R1864" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="S1864" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1865" s="1">
+        <v>46226.493206018517</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1865" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1865">
+        <v>2748940098</v>
+      </c>
+      <c r="G1865" s="2">
+        <v>1784818156356210</v>
+      </c>
+      <c r="H1865" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1865" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1865" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1865" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1865" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1865">
+        <v>19</v>
+      </c>
+      <c r="R1865" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1865" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1866" s="1">
+        <v>46226.49359953704</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1866" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1866">
+        <v>2772224023</v>
+      </c>
+      <c r="G1866" s="2">
+        <v>1784818247359060</v>
+      </c>
+      <c r="H1866" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1866" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1866" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1866" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1866" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1866" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1866">
+        <v>16</v>
+      </c>
+      <c r="R1866" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S1866" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1867" s="1">
+        <v>46226.494768518518</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1867" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1867">
+        <v>2766060969</v>
+      </c>
+      <c r="G1867" s="2">
+        <v>1784818348361600</v>
+      </c>
+      <c r="H1867" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1867" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1867" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1867" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1867" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1867">
+        <v>19</v>
+      </c>
+      <c r="R1867" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1867" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1868" s="1">
+        <v>46226.494884259257</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1868" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1868">
+        <v>2766060979</v>
+      </c>
+      <c r="G1868" s="2">
+        <v>1784818358361970</v>
+      </c>
+      <c r="H1868" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1868" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1868" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1868" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1868" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1868">
+        <v>19</v>
+      </c>
+      <c r="R1868" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S1868" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1869" s="1">
+        <v>46226.495486111111</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1869" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1869">
+        <v>2766061030</v>
+      </c>
+      <c r="G1869" s="2">
+        <v>1784818410363870</v>
+      </c>
+      <c r="H1869" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1869" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1869" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1869" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1869" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1869">
+        <v>19</v>
+      </c>
+      <c r="R1869" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S1869" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1870" s="1">
+        <v>46226.496423611112</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1870" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1870">
+        <v>2783247473</v>
+      </c>
+      <c r="G1870" s="2">
+        <v>1784818491366600</v>
+      </c>
+      <c r="H1870" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1870" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1870" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1870" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1870" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1870" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1870">
+        <v>16</v>
+      </c>
+      <c r="R1870" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1870" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1871" s="1">
+        <v>46226.496747685182</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1871" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1871">
+        <v>2783247501</v>
+      </c>
+      <c r="G1871" s="2">
+        <v>1784818519367790</v>
+      </c>
+      <c r="H1871" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1871" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1871" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1871" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1871" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1871" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1871">
+        <v>16</v>
+      </c>
+      <c r="R1871" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1871" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1872" s="1">
+        <v>46226.497175925928</v>
+      </c>
+      <c r="B1872" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1872" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1872">
+        <v>2783247539</v>
+      </c>
+      <c r="G1872" s="2">
+        <v>1784818556369440</v>
+      </c>
+      <c r="H1872" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1872" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1872" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1872" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1872" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1872">
+        <v>19</v>
+      </c>
+      <c r="R1872" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="S1872" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1873" s="1">
+        <v>46226.497812499998</v>
+      </c>
+      <c r="B1873" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1873" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1873">
+        <v>2783247593</v>
+      </c>
+      <c r="G1873" s="2">
+        <v>1784818611370890</v>
+      </c>
+      <c r="H1873" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1873" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1873" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1873" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1873" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1873" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1873">
+        <v>16</v>
+      </c>
+      <c r="R1873" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="S1873" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1874" s="1">
+        <v>46226.498599537037</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1874" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1874">
+        <v>2783247661</v>
+      </c>
+      <c r="G1874" s="2">
+        <v>1784818679372530</v>
+      </c>
+      <c r="H1874" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1874" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1874" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1874" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1874" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1874">
+        <v>19</v>
+      </c>
+      <c r="R1874" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1874" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1875" s="1">
+        <v>46226.499166666668</v>
+      </c>
+      <c r="B1875" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1875" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1875">
+        <v>2766244291</v>
+      </c>
+      <c r="G1875" s="2">
+        <v>1784818728373950</v>
+      </c>
+      <c r="H1875" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1875" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1875" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1875" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1875" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1875" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1875">
+        <v>16</v>
+      </c>
+      <c r="R1875" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1875" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1876" s="1">
+        <v>46226.499594907407</v>
+      </c>
+      <c r="B1876" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1876" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1876">
+        <v>2766244328</v>
+      </c>
+      <c r="G1876" s="2">
+        <v>1784818765374850</v>
+      </c>
+      <c r="H1876" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1876" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1876" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1876" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1876" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1876" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1876">
+        <v>16</v>
+      </c>
+      <c r="R1876" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1876" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1877" s="1">
+        <v>46226.500300925924</v>
+      </c>
+      <c r="B1877" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1877" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1877">
+        <v>2783304218</v>
+      </c>
+      <c r="G1877" s="2">
+        <v>1784818826376710</v>
+      </c>
+      <c r="H1877" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1877" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1877" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1877" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1877" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1877" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1877">
+        <v>16</v>
+      </c>
+      <c r="R1877" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1877" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1878" s="1">
+        <v>46226.500497685185</v>
+      </c>
+      <c r="B1878" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1878" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1878">
+        <v>2783304235</v>
+      </c>
+      <c r="G1878" s="2">
+        <v>1784818843377110</v>
+      </c>
+      <c r="H1878" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1878" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1878" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1878" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1878" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1878" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1878">
+        <v>16</v>
+      </c>
+      <c r="R1878" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1878" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1879" s="1">
+        <v>46226.501006944447</v>
+      </c>
+      <c r="B1879" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1879" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1879">
+        <v>2780049973</v>
+      </c>
+      <c r="G1879" s="2">
+        <v>1784818887377890</v>
+      </c>
+      <c r="H1879" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1879" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1879" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1879" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1879" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1879">
+        <v>19</v>
+      </c>
+      <c r="R1879" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1879" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1880" s="1">
+        <v>46226.501157407409</v>
+      </c>
+      <c r="B1880" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1880" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1880">
+        <v>2780049985</v>
+      </c>
+      <c r="G1880" s="2">
+        <v>1784818900378150</v>
+      </c>
+      <c r="H1880" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1880" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1880" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1880" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1880" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1880">
+        <v>19</v>
+      </c>
+      <c r="R1880" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1880" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1881" s="1">
+        <v>46226.502060185187</v>
+      </c>
+      <c r="B1881" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1881" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1881">
+        <v>2780050063</v>
+      </c>
+      <c r="G1881" s="2">
+        <v>1784818978380090</v>
+      </c>
+      <c r="H1881" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1881" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1881" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1881" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1881" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1881">
+        <v>19</v>
+      </c>
+      <c r="R1881" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S1881" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1882" s="1">
+        <v>46226.50304398148</v>
+      </c>
+      <c r="B1882" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1882" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1882">
+        <v>2749050822</v>
+      </c>
+      <c r="G1882" s="2">
+        <v>1784819063381800</v>
+      </c>
+      <c r="H1882" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1882" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1882" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1882" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1882" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1882" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1882">
+        <v>16</v>
+      </c>
+      <c r="R1882" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="S1882" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1883" s="1">
+        <v>46226.504756944443</v>
+      </c>
+      <c r="B1883" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1883" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1883">
+        <v>2749302132</v>
+      </c>
+      <c r="G1883" s="2">
+        <v>1784819211385880</v>
+      </c>
+      <c r="H1883" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1883" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1883" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1883" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1883" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1883">
+        <v>19</v>
+      </c>
+      <c r="R1883" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1883" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1884" s="1">
+        <v>46226.504872685182</v>
+      </c>
+      <c r="B1884" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1884" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1884">
+        <v>2749302142</v>
+      </c>
+      <c r="G1884" s="2">
+        <v>1784819221386160</v>
+      </c>
+      <c r="H1884" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1884" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1884" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1884" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1884" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1884">
+        <v>19</v>
+      </c>
+      <c r="R1884" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1884" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1885" s="1">
+        <v>46226.504976851851</v>
+      </c>
+      <c r="B1885" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1885" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1885">
+        <v>2749302151</v>
+      </c>
+      <c r="G1885" s="2">
+        <v>1784819230386450</v>
+      </c>
+      <c r="H1885" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1885" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1885" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1885" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1885" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1885">
+        <v>19</v>
+      </c>
+      <c r="R1885" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1885" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1886" s="1">
+        <v>46226.505358796298</v>
+      </c>
+      <c r="B1886" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1886" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1886">
+        <v>2783889015</v>
+      </c>
+      <c r="G1886" s="2">
+        <v>1784819263387530</v>
+      </c>
+      <c r="H1886" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1886" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1886" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1886" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1886" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1886" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1886">
+        <v>16</v>
+      </c>
+      <c r="R1886" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1886" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1887" s="1">
+        <v>46226.507268518515</v>
+      </c>
+      <c r="B1887" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1887" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1887">
+        <v>2782092536</v>
+      </c>
+      <c r="G1887" s="2">
+        <v>1784819428392580</v>
+      </c>
+      <c r="H1887" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1887" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1887" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1887" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1887" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1887">
+        <v>19</v>
+      </c>
+      <c r="R1887" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1887" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1888" s="1">
+        <v>46226.50818287037</v>
+      </c>
+      <c r="B1888" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1888" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1888">
+        <v>2758379490</v>
+      </c>
+      <c r="G1888" s="2">
+        <v>1784819507394630</v>
+      </c>
+      <c r="H1888" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1888" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1888" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1888" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1888" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1888">
+        <v>19</v>
+      </c>
+      <c r="R1888" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1888" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1889" s="1">
+        <v>46226.508414351854</v>
+      </c>
+      <c r="B1889" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1889" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1889">
+        <v>2782092635</v>
+      </c>
+      <c r="G1889" s="2">
+        <v>1784819527395080</v>
+      </c>
+      <c r="H1889" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1889" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1889" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1889" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1889" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1889">
+        <v>19</v>
+      </c>
+      <c r="R1889" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1889" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1890" s="1">
+        <v>46226.508738425924</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1890" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1890">
+        <v>2758379538</v>
+      </c>
+      <c r="G1890" s="2">
+        <v>1784819555395950</v>
+      </c>
+      <c r="H1890" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1890" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1890" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1890" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1890" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1890">
+        <v>19</v>
+      </c>
+      <c r="R1890" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1890" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1891" s="1">
+        <v>46226.509351851855</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1891" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1891">
+        <v>2777611436</v>
+      </c>
+      <c r="G1891" s="2">
+        <v>1784819608397430</v>
+      </c>
+      <c r="H1891" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1891" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1891" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1891" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1891" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1891" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1891">
+        <v>16</v>
+      </c>
+      <c r="R1891" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1891" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1892" s="1">
+        <v>46226.509837962964</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1892" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1892">
+        <v>2777611478</v>
+      </c>
+      <c r="G1892" s="2">
+        <v>1784819650398660</v>
+      </c>
+      <c r="H1892" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1892" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1892" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1892" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1892" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1892">
+        <v>19</v>
+      </c>
+      <c r="R1892" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1892" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1893" s="1">
+        <v>46226.509988425925</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1893" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1893">
+        <v>2777611491</v>
+      </c>
+      <c r="G1893" s="2">
+        <v>1784819663399180</v>
+      </c>
+      <c r="H1893" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1893" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1893" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1893" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1893" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1893" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1893">
+        <v>16</v>
+      </c>
+      <c r="R1893" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1893" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1894" s="1">
+        <v>46226.511099537034</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1894" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1894">
+        <v>2748932782</v>
+      </c>
+      <c r="G1894" s="2">
+        <v>1784819759401880</v>
+      </c>
+      <c r="H1894" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1894" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1894" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1894" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1894" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1894">
+        <v>19</v>
+      </c>
+      <c r="R1894" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1894" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1895" s="1">
+        <v>46226.511296296296</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1895" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1895">
+        <v>2748932799</v>
+      </c>
+      <c r="G1895" s="2">
+        <v>1784819776402310</v>
+      </c>
+      <c r="H1895" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1895" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1895" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1895" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1895" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1895" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1895">
+        <v>16</v>
+      </c>
+      <c r="R1895" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1895" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1896" s="1">
+        <v>46226.511574074073</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1896" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1896">
+        <v>2748932823</v>
+      </c>
+      <c r="G1896" s="2">
+        <v>1784819800403050</v>
+      </c>
+      <c r="H1896" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1896" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1896" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1896" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1896" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1896">
+        <v>19</v>
+      </c>
+      <c r="R1896" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1896" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1897" s="1">
+        <v>46226.512187499997</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1897" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1897">
+        <v>2749411924</v>
+      </c>
+      <c r="G1897" s="2">
+        <v>1784819853404410</v>
+      </c>
+      <c r="H1897" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1897" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1897" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1897" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1897" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1897" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1897">
+        <v>16</v>
+      </c>
+      <c r="R1897" s="3">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="S1897" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1898" s="1">
+        <v>46226.515752314815</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1898" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1898">
+        <v>2784264533</v>
+      </c>
+      <c r="G1898" s="2">
+        <v>1784820161411050</v>
+      </c>
+      <c r="H1898" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1898" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1898" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1898" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1898" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1898" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1898">
+        <v>16</v>
+      </c>
+      <c r="R1898" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="S1898" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1899" s="1">
+        <v>46226.516631944447</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1899" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1899">
+        <v>2784264609</v>
+      </c>
+      <c r="G1899" s="2">
+        <v>1784820237413930</v>
+      </c>
+      <c r="H1899" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1899" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1899" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1899" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1899" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1899" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1899">
+        <v>16</v>
+      </c>
+      <c r="R1899" s="3">
+        <v>4.0972222222222226E-3</v>
+      </c>
+      <c r="S1899" s="3">
+        <v>3.8888888888888888E-3</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1900" s="1">
+        <v>46226.52244212963</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1900" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1900">
+        <v>2777593665</v>
+      </c>
+      <c r="G1900" s="2">
+        <v>1784820739427950</v>
+      </c>
+      <c r="H1900" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1900" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1900" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1900" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1900" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1900" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1900">
+        <v>16</v>
+      </c>
+      <c r="R1900" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1900" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1901" s="1">
+        <v>46226.522685185184</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1901" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1901">
+        <v>2777593686</v>
+      </c>
+      <c r="G1901" s="2">
+        <v>1784820760428290</v>
+      </c>
+      <c r="H1901" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1901" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1901" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1901" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1901" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1901" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1901">
+        <v>16</v>
+      </c>
+      <c r="R1901" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1901" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1902" s="1">
+        <v>46226.527106481481</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1902" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1902">
+        <v>2749052901</v>
+      </c>
+      <c r="G1902" s="2">
+        <v>1784821142436100</v>
+      </c>
+      <c r="H1902" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1902" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1902" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1902" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1902" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1902" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1902">
+        <v>16</v>
+      </c>
+      <c r="R1902" s="3">
+        <v>3.6342592592592594E-3</v>
+      </c>
+      <c r="S1902" s="3">
+        <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1903" s="1">
+        <v>46226.588252314818</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1903" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1903">
+        <v>2752532495</v>
+      </c>
+      <c r="G1903" s="2">
+        <v>1784826373580260</v>
+      </c>
+      <c r="H1903" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1903" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1903" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1903" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1903" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1903">
+        <v>19</v>
+      </c>
+      <c r="R1903" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1903" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1904" s="1">
+        <v>46226.589108796295</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1904" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1904">
+        <v>2752532571</v>
+      </c>
+      <c r="G1904" s="2">
+        <v>1784826449581840</v>
+      </c>
+      <c r="H1904" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1904" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1904" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1904" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1904" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1904">
+        <v>19</v>
+      </c>
+      <c r="R1904" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1904" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1905" s="1">
+        <v>46226.590474537035</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1905" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1905">
+        <v>2749351346</v>
+      </c>
+      <c r="G1905" s="2">
+        <v>1784826617586270</v>
+      </c>
+      <c r="H1905" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1905" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1905" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1905" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1905" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1905">
+        <v>19</v>
+      </c>
+      <c r="R1905" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1905" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1906" s="1">
+        <v>46226.591678240744</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1906" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1906">
+        <v>2749351397</v>
+      </c>
+      <c r="G1906" s="2">
+        <v>1784826669588250</v>
+      </c>
+      <c r="H1906" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1906" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1906" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1906" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1906" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1906">
+        <v>19</v>
+      </c>
+      <c r="R1906" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1906" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1907" s="1">
+        <v>46226.594733796293</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1907" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1907">
+        <v>2778345323</v>
+      </c>
+      <c r="G1907" s="2">
+        <v>1784826985599050</v>
+      </c>
+      <c r="H1907" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1907" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1907" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1907" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1907" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1907" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1907">
+        <v>16</v>
+      </c>
+      <c r="R1907" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="S1907" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1908" s="1">
+        <v>46226.595150462963</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1908" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1908">
+        <v>2778345359</v>
+      </c>
+      <c r="G1908" s="2">
+        <v>1784827021600420</v>
+      </c>
+      <c r="H1908" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1908" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1908" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1908" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1908" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1908">
+        <v>19</v>
+      </c>
+      <c r="R1908" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1908" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1909" s="1">
+        <v>46226.595590277779</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1909" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1909">
+        <v>1822817384</v>
+      </c>
+      <c r="G1909" s="2">
+        <v>1784827059601510</v>
+      </c>
+      <c r="H1909" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1909" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1909" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1909" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1909" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1909">
+        <v>19</v>
+      </c>
+      <c r="R1909" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1909" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1910" s="1">
+        <v>46226.595694444448</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1910" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1910">
+        <v>1822817392</v>
+      </c>
+      <c r="G1910" s="2">
+        <v>1784827068601780</v>
+      </c>
+      <c r="H1910" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1910" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1910" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1910" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1910" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1910">
+        <v>19</v>
+      </c>
+      <c r="R1910" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1910" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1911" s="1">
+        <v>46226.595810185187</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1911" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1911">
+        <v>1822817402</v>
+      </c>
+      <c r="G1911" s="2">
+        <v>1784827078602420</v>
+      </c>
+      <c r="H1911" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1911" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1911" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1911" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1911" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1911">
+        <v>19</v>
+      </c>
+      <c r="R1911" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S1911" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1912" s="1">
+        <v>46226.595902777779</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1912" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1912">
+        <v>1822817410</v>
+      </c>
+      <c r="G1912" s="2">
+        <v>1784827086602850</v>
+      </c>
+      <c r="H1912" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1912" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1912" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1912" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1912" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1912">
+        <v>19</v>
+      </c>
+      <c r="R1912" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1912" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1913" s="1">
+        <v>46226.596585648149</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1913" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1913">
+        <v>2784665673</v>
+      </c>
+      <c r="G1913" s="2">
+        <v>1784827145605570</v>
+      </c>
+      <c r="H1913" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1913" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1913" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1913" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1913" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1913" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1913">
+        <v>16</v>
+      </c>
+      <c r="R1913" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="S1913" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1914" s="1">
+        <v>46226.599537037036</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1914" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1914">
+        <v>1809351657</v>
+      </c>
+      <c r="G1914" s="2">
+        <v>1784827398613140</v>
+      </c>
+      <c r="H1914" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1914" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1914" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1914" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1914" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1914">
+        <v>19</v>
+      </c>
+      <c r="R1914" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1914" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1915" s="1">
+        <v>46226.599710648145</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1915" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1915">
+        <v>1809351673</v>
+      </c>
+      <c r="G1915" s="2">
+        <v>1784827414613570</v>
+      </c>
+      <c r="H1915" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1915" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1915" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1915" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1915" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1915">
+        <v>21</v>
+      </c>
+      <c r="R1915" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1915" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1916" s="1">
+        <v>46226.599872685183</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1916" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1916">
+        <v>1809351687</v>
+      </c>
+      <c r="G1916" s="2">
+        <v>1784827428614070</v>
+      </c>
+      <c r="H1916" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1916" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1916" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1916" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1916" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1916">
+        <v>19</v>
+      </c>
+      <c r="R1916" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1916" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1917" s="1">
+        <v>46226.60050925926</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1917" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1917">
+        <v>1809351742</v>
+      </c>
+      <c r="G1917" s="2">
+        <v>1784827483615480</v>
+      </c>
+      <c r="H1917" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1917" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1917" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1917" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1917" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1917">
+        <v>19</v>
+      </c>
+      <c r="R1917" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1917" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1918" s="1">
+        <v>46226.600856481484</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1918" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1918">
+        <v>2784820880</v>
+      </c>
+      <c r="G1918" s="2">
+        <v>1784827514616590</v>
+      </c>
+      <c r="H1918" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1918" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1918" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1918" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1918" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1918">
+        <v>19</v>
+      </c>
+      <c r="R1918" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1918" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1919" s="1">
+        <v>46226.600995370369</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1919" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1919">
+        <v>2784820893</v>
+      </c>
+      <c r="G1919" s="2">
+        <v>1784827526617110</v>
+      </c>
+      <c r="H1919" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1919" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1919" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1919" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1919" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1919">
+        <v>19</v>
+      </c>
+      <c r="R1919" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1919" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1920" s="1">
+        <v>46226.601134259261</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1920" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1920">
+        <v>2784820904</v>
+      </c>
+      <c r="G1920" s="2">
+        <v>1784827538617650</v>
+      </c>
+      <c r="H1920" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1920" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1920" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1920" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1920" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1920">
+        <v>19</v>
+      </c>
+      <c r="R1920" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1920" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1921" s="1">
+        <v>46226.60125</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1921" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1921">
+        <v>2784820914</v>
+      </c>
+      <c r="G1921" s="2">
+        <v>1784827548618180</v>
+      </c>
+      <c r="H1921" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1921" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1921" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1921" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1921" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1921">
+        <v>19</v>
+      </c>
+      <c r="R1921" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1921" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1922" s="1">
+        <v>46226.601701388892</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1922" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1922">
+        <v>2748949529</v>
+      </c>
+      <c r="G1922" s="2">
+        <v>1784827587619610</v>
+      </c>
+      <c r="H1922" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1922" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1922" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1922" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1922" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1922">
+        <v>19</v>
+      </c>
+      <c r="R1922" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1922" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1923" s="1">
+        <v>46226.602118055554</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1923" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1923">
+        <v>2748949565</v>
+      </c>
+      <c r="G1923" s="2">
+        <v>1784827623620960</v>
+      </c>
+      <c r="H1923" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1923" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1923" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1923" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1923" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1923">
+        <v>19</v>
+      </c>
+      <c r="R1923" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1923" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1924" s="1">
+        <v>46226.602835648147</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1924" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1924">
+        <v>2772233461</v>
+      </c>
+      <c r="G1924" s="2">
+        <v>1784827685623500</v>
+      </c>
+      <c r="H1924" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1924" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1924" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1924" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1924" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1924" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1924">
+        <v>16</v>
+      </c>
+      <c r="R1924" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S1924" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1925" s="1">
+        <v>46226.603530092594</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1925" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1925">
+        <v>2766070366</v>
+      </c>
+      <c r="G1925" s="2">
+        <v>1784827745625940</v>
+      </c>
+      <c r="H1925" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1925" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1925" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1925" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1925" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1925">
+        <v>19</v>
+      </c>
+      <c r="R1925" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1925" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1926" s="1">
+        <v>46226.603634259256</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1926" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1926">
+        <v>2766070375</v>
+      </c>
+      <c r="G1926" s="2">
+        <v>1784827754626310</v>
+      </c>
+      <c r="H1926" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1926" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1926" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1926" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1926" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1926">
+        <v>19</v>
+      </c>
+      <c r="R1926" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S1926" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1927" s="1">
+        <v>46226.603888888887</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1927" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1927">
+        <v>2766070396</v>
+      </c>
+      <c r="G1927" s="2">
+        <v>1784827776626900</v>
+      </c>
+      <c r="H1927" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1927" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1927" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1927" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1927" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1927">
+        <v>19</v>
+      </c>
+      <c r="R1927" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1927" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1928" s="1">
+        <v>46226.604270833333</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1928" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1928">
+        <v>2766070429</v>
+      </c>
+      <c r="G1928" s="2">
+        <v>1784827809627890</v>
+      </c>
+      <c r="H1928" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1928" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1928" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1928" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1928" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1928">
+        <v>19</v>
+      </c>
+      <c r="R1928" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1928" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1929" s="1">
+        <v>46226.605057870373</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1929" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1929">
+        <v>2783256859</v>
+      </c>
+      <c r="G1929" s="2">
+        <v>1784827877630450</v>
+      </c>
+      <c r="H1929" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1929" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1929" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1929" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1929" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1929" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1929">
+        <v>16</v>
+      </c>
+      <c r="R1929" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1929" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1930" s="1">
+        <v>46226.60560185185</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1930" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1930">
+        <v>2783256906</v>
+      </c>
+      <c r="G1930" s="2">
+        <v>1784827924632170</v>
+      </c>
+      <c r="H1930" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1930" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1930" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1930" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1930" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1930" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1930">
+        <v>16</v>
+      </c>
+      <c r="R1930" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="S1930" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1931" s="1">
+        <v>46226.606782407405</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1931" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1931">
+        <v>2766253589</v>
+      </c>
+      <c r="G1931" s="2">
+        <v>1784828026634960</v>
+      </c>
+      <c r="H1931" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1931" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1931" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1931" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1931" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1931" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1931">
+        <v>16</v>
+      </c>
+      <c r="R1931" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1931" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1932" s="1">
+        <v>46226.608425925922</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1932" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1932">
+        <v>2766253731</v>
+      </c>
+      <c r="G1932" s="2">
+        <v>1784828168639190</v>
+      </c>
+      <c r="H1932" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1932" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1932" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1932" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1932" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1932">
+        <v>19</v>
+      </c>
+      <c r="R1932" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1932" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1933" s="1">
+        <v>46226.6090625</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1933" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1933">
+        <v>2766253787</v>
+      </c>
+      <c r="G1933" s="2">
+        <v>1784828223640650</v>
+      </c>
+      <c r="H1933" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1933" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1933" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1933" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1933" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1933" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1933">
+        <v>16</v>
+      </c>
+      <c r="R1933" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1933" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1934" s="1">
+        <v>46226.610474537039</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1934" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1934">
+        <v>2783313737</v>
+      </c>
+      <c r="G1934" s="2">
+        <v>1784828345644410</v>
+      </c>
+      <c r="H1934" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1934" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1934" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1934" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1934" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1934" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1934">
+        <v>16</v>
+      </c>
+      <c r="R1934" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1934" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1935" s="1">
+        <v>46226.611087962963</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1935" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1935">
+        <v>2783313790</v>
+      </c>
+      <c r="G1935" s="2">
+        <v>1784828398645750</v>
+      </c>
+      <c r="H1935" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1935" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1935" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1935" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1935" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1935">
+        <v>19</v>
+      </c>
+      <c r="R1935" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1935" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1936" s="1">
+        <v>46226.611701388887</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1936" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1936">
+        <v>2780059536</v>
+      </c>
+      <c r="G1936" s="2">
+        <v>1784828451648420</v>
+      </c>
+      <c r="H1936" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1936" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1936" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1936" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1936" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1936">
+        <v>19</v>
+      </c>
+      <c r="R1936" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1936" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1937" s="1">
+        <v>46226.611875000002</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1937" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1937">
+        <v>2780059551</v>
+      </c>
+      <c r="G1937" s="2">
+        <v>1784828466648880</v>
+      </c>
+      <c r="H1937" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1937" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1937" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1937" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1937" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1937">
+        <v>19</v>
+      </c>
+      <c r="R1937" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1937" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1938" s="1">
+        <v>46226.612025462964</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1938" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1938">
+        <v>2780059564</v>
+      </c>
+      <c r="G1938" s="2">
+        <v>1784828479649510</v>
+      </c>
+      <c r="H1938" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1938" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1938" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1938" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1938" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1938">
+        <v>19</v>
+      </c>
+      <c r="R1938" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1938" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1939" s="1">
+        <v>46226.612719907411</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1939" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1939">
+        <v>2780059624</v>
+      </c>
+      <c r="G1939" s="2">
+        <v>1784828539651930</v>
+      </c>
+      <c r="H1939" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1939" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1939" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1939" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1939" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1939">
+        <v>19</v>
+      </c>
+      <c r="R1939" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1939" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1940" s="1">
+        <v>46226.612905092596</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1940" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1940">
+        <v>2780059640</v>
+      </c>
+      <c r="G1940" s="2">
+        <v>1784828555652590</v>
+      </c>
+      <c r="H1940" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1940" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1940" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1940" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1940" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1940">
+        <v>19</v>
+      </c>
+      <c r="R1940" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1940" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1941" s="1">
+        <v>46226.613622685189</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1941" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1941">
+        <v>2749311538</v>
+      </c>
+      <c r="G1941" s="2">
+        <v>1784828617653970</v>
+      </c>
+      <c r="H1941" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1941" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1941" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1941" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1941" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1941">
+        <v>19</v>
+      </c>
+      <c r="R1941" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1941" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1942" s="1">
+        <v>46226.613865740743</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1942" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1942">
+        <v>2749311559</v>
+      </c>
+      <c r="G1942" s="2">
+        <v>1784828638654700</v>
+      </c>
+      <c r="H1942" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1942" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1942" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1942" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1942" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1942">
+        <v>19</v>
+      </c>
+      <c r="R1942" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1942" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1943" s="1">
+        <v>46226.614074074074</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1943" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1943">
+        <v>2749311577</v>
+      </c>
+      <c r="G1943" s="2">
+        <v>1784828656655310</v>
+      </c>
+      <c r="H1943" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1943" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1943" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1943" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1943" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1943" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1943">
+        <v>16</v>
+      </c>
+      <c r="R1943" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1943" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1944" s="1">
+        <v>46226.614733796298</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1944" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1944">
+        <v>2783898465</v>
+      </c>
+      <c r="G1944" s="2">
+        <v>1784828713657680</v>
+      </c>
+      <c r="H1944" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1944" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1944" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1944" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1944" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1944" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1944">
+        <v>16</v>
+      </c>
+      <c r="R1944" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S1944" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1945" s="1">
+        <v>46226.615486111114</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1945" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1945">
+        <v>2783898530</v>
+      </c>
+      <c r="G1945" s="2">
+        <v>1784828778660380</v>
+      </c>
+      <c r="H1945" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1945" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1945" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1945" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1945" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1945">
+        <v>19</v>
+      </c>
+      <c r="R1945" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1945" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1946" s="1">
+        <v>46226.616516203707</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1946" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1946">
+        <v>2782101975</v>
+      </c>
+      <c r="G1946" s="2">
+        <v>1784828867663460</v>
+      </c>
+      <c r="H1946" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1946" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1946" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1946" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1946" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1946" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1946">
+        <v>16</v>
+      </c>
+      <c r="R1946" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1946" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1947" s="1">
+        <v>46226.617106481484</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1947" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1947">
+        <v>2758388901</v>
+      </c>
+      <c r="G1947" s="2">
+        <v>1784828918665400</v>
+      </c>
+      <c r="H1947" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1947" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1947" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1947" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1947" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1947">
+        <v>19</v>
+      </c>
+      <c r="R1947" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1947" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1948" s="1">
+        <v>46226.617476851854</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1948" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1948">
+        <v>2758388933</v>
+      </c>
+      <c r="G1948" s="2">
+        <v>1784828950666480</v>
+      </c>
+      <c r="H1948" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1948" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1948" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1948" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1948" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1948">
+        <v>19</v>
+      </c>
+      <c r="R1948" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1948" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1949" s="1">
+        <v>46226.617951388886</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1949" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1949">
+        <v>2777620819</v>
+      </c>
+      <c r="G1949" s="2">
+        <v>1784828991668480</v>
+      </c>
+      <c r="H1949" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1949" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1949" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1949" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1949" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1949">
+        <v>19</v>
+      </c>
+      <c r="R1949" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1949" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1950" s="1">
+        <v>46226.618113425924</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1950" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1950">
+        <v>2777620833</v>
+      </c>
+      <c r="G1950" s="2">
+        <v>1784829005669240</v>
+      </c>
+      <c r="H1950" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1950" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1950" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1950" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1950" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1950">
+        <v>19</v>
+      </c>
+      <c r="R1950" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1950" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1951" s="1">
+        <v>46226.618819444448</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1951" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1951">
+        <v>2748942089</v>
+      </c>
+      <c r="G1951" s="2">
+        <v>1784829066671520</v>
+      </c>
+      <c r="H1951" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1951" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1951" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1951" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1951" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1951" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1951">
+        <v>16</v>
+      </c>
+      <c r="R1951" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1951" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1952" s="1">
+        <v>46226.619189814817</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1952" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1952">
+        <v>2748942121</v>
+      </c>
+      <c r="G1952" s="2">
+        <v>1784829098672630</v>
+      </c>
+      <c r="H1952" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1952" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1952" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1952" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1952" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1952" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1952">
+        <v>16</v>
+      </c>
+      <c r="R1952" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1952" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1953" s="1">
+        <v>46226.619710648149</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1953" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1953">
+        <v>2777602069</v>
+      </c>
+      <c r="G1953" s="2">
+        <v>1784829143674710</v>
+      </c>
+      <c r="H1953" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1953" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1953" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1953" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1953" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1953" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1953">
+        <v>16</v>
+      </c>
+      <c r="R1953" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1953" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1954" s="1">
+        <v>46226.619942129626</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1954" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1954">
+        <v>2777602089</v>
+      </c>
+      <c r="G1954" s="2">
+        <v>1784829163675400</v>
+      </c>
+      <c r="H1954" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1954" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1954" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1954" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1954" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1954" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1954">
+        <v>16</v>
+      </c>
+      <c r="R1954" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1954" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1955" s="1">
+        <v>46226.620115740741</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1955" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1955">
+        <v>2777602104</v>
+      </c>
+      <c r="G1955" s="2">
+        <v>1784829178675980</v>
+      </c>
+      <c r="H1955" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1955" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1955" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1955" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1955" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1955" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1955">
+        <v>16</v>
+      </c>
+      <c r="R1955" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1955" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1956" s="1">
+        <v>46226.62462962963</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1956" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1956">
+        <v>2777602494</v>
+      </c>
+      <c r="G1956" s="2">
+        <v>1784829568689310</v>
+      </c>
+      <c r="H1956" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1956" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1956" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1956" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1956" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1956" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1956">
+        <v>16</v>
+      </c>
+      <c r="R1956" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1956" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1957" s="1">
+        <v>46226.625393518516</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1957" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1957">
+        <v>2764815645</v>
+      </c>
+      <c r="G1957" s="2">
+        <v>1784829634690960</v>
+      </c>
+      <c r="H1957" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1957" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1957" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1957" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1957" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1957">
+        <v>19</v>
+      </c>
+      <c r="R1957" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1957" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1958" s="1">
+        <v>46226.625601851854</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1958" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1958">
+        <v>2764815663</v>
+      </c>
+      <c r="G1958" s="2">
+        <v>1784829652691540</v>
+      </c>
+      <c r="H1958" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1958" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1958" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1958" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1958" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1958" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1958">
+        <v>16</v>
+      </c>
+      <c r="R1958" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S1958" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1959" s="1">
+        <v>46226.626666666663</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1959" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1959">
+        <v>2778692946</v>
+      </c>
+      <c r="G1959" s="2">
+        <v>1784829744694670</v>
+      </c>
+      <c r="H1959" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1959" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1959" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1959" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1959" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1959">
+        <v>19</v>
+      </c>
+      <c r="R1959" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S1959" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1960" s="1">
+        <v>46226.627187500002</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1960" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1960">
+        <v>2778692991</v>
+      </c>
+      <c r="G1960" s="2">
+        <v>1784829789696080</v>
+      </c>
+      <c r="H1960" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1960" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1960" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1960" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1960" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1960">
+        <v>19</v>
+      </c>
+      <c r="R1960" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1960" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1961" s="1">
+        <v>46226.627743055556</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1961" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1961">
+        <v>2782407268</v>
+      </c>
+      <c r="G1961" s="2">
+        <v>1784829837697400</v>
+      </c>
+      <c r="H1961" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1961" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1961" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1961" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1961" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1961">
+        <v>19</v>
+      </c>
+      <c r="R1961" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1961" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1962" s="1">
+        <v>46226.628449074073</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1962" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1962">
+        <v>2782407329</v>
+      </c>
+      <c r="G1962" s="2">
+        <v>1784829898699370</v>
+      </c>
+      <c r="H1962" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1962" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1962" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1962" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1962" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1962">
+        <v>19</v>
+      </c>
+      <c r="R1962" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1962" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1963" s="1">
+        <v>46226.629282407404</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1963" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1963">
+        <v>2772730181</v>
+      </c>
+      <c r="G1963" s="2">
+        <v>1784829970701960</v>
+      </c>
+      <c r="H1963" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1963" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1963" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1963" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1963" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1963">
+        <v>19</v>
+      </c>
+      <c r="R1963" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1963" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1964" s="1">
+        <v>46226.629479166666</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1964" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1964">
+        <v>2772730198</v>
+      </c>
+      <c r="G1964" s="2">
+        <v>1784829987702510</v>
+      </c>
+      <c r="H1964" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1964" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1964" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1964" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1964" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1964">
+        <v>19</v>
+      </c>
+      <c r="R1964" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1964" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1965" s="1">
+        <v>46226.631331018521</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1965" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1965">
+        <v>2784441074</v>
+      </c>
+      <c r="G1965" s="2">
+        <v>1784830147708170</v>
+      </c>
+      <c r="H1965" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1965" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1965" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1965" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1965" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1965" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1965">
+        <v>16</v>
+      </c>
+      <c r="R1965" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S1965" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1966" s="1">
+        <v>46226.632094907407</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1966" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1966">
+        <v>2783092407</v>
+      </c>
+      <c r="G1966" s="2">
+        <v>1784830213709950</v>
+      </c>
+      <c r="H1966" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1966" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1966" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1966" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1966" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1966">
+        <v>19</v>
+      </c>
+      <c r="R1966" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1966" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1967" s="1">
+        <v>46226.632256944446</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1967" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1967">
+        <v>2783092420</v>
+      </c>
+      <c r="G1967" s="2">
+        <v>1784830227710500</v>
+      </c>
+      <c r="H1967" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1967" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1967" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1967" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1967" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1967">
+        <v>19</v>
+      </c>
+      <c r="R1967" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1967" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1968" s="1">
+        <v>46226.632407407407</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1968" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1968">
+        <v>2783092434</v>
+      </c>
+      <c r="G1968" s="2">
+        <v>1784830240711090</v>
+      </c>
+      <c r="H1968" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1968" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1968" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1968" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1968" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1968" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1968">
+        <v>16</v>
+      </c>
+      <c r="R1968" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1968" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1969" s="1">
+        <v>46226.633020833331</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1969" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1969">
+        <v>2782437400</v>
+      </c>
+      <c r="G1969" s="2">
+        <v>1784830293713100</v>
+      </c>
+      <c r="H1969" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1969" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1969" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1969" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1969" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1969" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1969">
+        <v>16</v>
+      </c>
+      <c r="R1969" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="S1969" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1970" s="1">
+        <v>46226.634548611109</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1970" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1970">
+        <v>2782984926</v>
+      </c>
+      <c r="G1970" s="2">
+        <v>1784830391716800</v>
+      </c>
+      <c r="H1970" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1970" t="s">
+        <v>170</v>
+      </c>
+      <c r="J1970" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1970" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1970" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1970">
+        <v>19</v>
+      </c>
+      <c r="R1970" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1970" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1971" s="1">
+        <v>46226.635208333333</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1971" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1971">
+        <v>2782984968</v>
+      </c>
+      <c r="G1971" s="2">
+        <v>1784830433718060</v>
+      </c>
+      <c r="H1971" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1971" t="s">
+        <v>170</v>
+      </c>
+      <c r="J1971" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1971" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1971" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1971">
+        <v>19</v>
+      </c>
+      <c r="R1971" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1971" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1972" s="1">
+        <v>46226.636111111111</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1972" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1972">
+        <v>2784788672</v>
+      </c>
+      <c r="G1972" s="2">
+        <v>1784830560721780</v>
+      </c>
+      <c r="H1972" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1972" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1972" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1972" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1972" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1972">
+        <v>19</v>
+      </c>
+      <c r="R1972" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1972" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1973" s="1">
+        <v>46226.636608796296</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1973" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1973">
+        <v>2783927711</v>
+      </c>
+      <c r="G1973" s="2">
+        <v>1784830603723590</v>
+      </c>
+      <c r="H1973" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1973" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1973" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1973" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1973" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1973" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1973">
+        <v>16</v>
+      </c>
+      <c r="R1973" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="S1973" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1974" s="1">
+        <v>46226.637361111112</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1974" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1974">
+        <v>2783927776</v>
+      </c>
+      <c r="G1974" s="2">
+        <v>1784830668726010</v>
+      </c>
+      <c r="H1974" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1974" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1974" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1974" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1974" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1974" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1974">
+        <v>16</v>
+      </c>
+      <c r="R1974" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1974" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1975" s="1">
+        <v>46226.638124999998</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1975" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1975">
+        <v>2784653893</v>
+      </c>
+      <c r="G1975" s="2">
+        <v>1784830734728920</v>
+      </c>
+      <c r="H1975" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1975" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1975" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1975" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1975" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1975">
+        <v>19</v>
+      </c>
+      <c r="R1975" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1975" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1976" s="1">
+        <v>46226.63863425926</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1976" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1976">
+        <v>2784653937</v>
+      </c>
+      <c r="G1976" s="2">
+        <v>1784830778730590</v>
+      </c>
+      <c r="H1976" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1976" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1976" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1976" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1976" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1976" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1976">
+        <v>16</v>
+      </c>
+      <c r="R1976" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="S1976" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1977" s="1">
+        <v>46226.639745370368</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1977" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1977">
+        <v>2749355602</v>
+      </c>
+      <c r="G1977" s="2">
+        <v>1784830874733360</v>
+      </c>
+      <c r="H1977" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1977" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1977" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1977" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1977" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1977" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1977">
+        <v>16</v>
+      </c>
+      <c r="R1977" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="S1977" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1978" s="1">
+        <v>46226.648831018516</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1978" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1978">
+        <v>2773284846</v>
+      </c>
+      <c r="G1978" s="2">
+        <v>1784831659759000</v>
+      </c>
+      <c r="H1978" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1978" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1978" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1978" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1978" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1978" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1978">
+        <v>16</v>
+      </c>
+      <c r="R1978" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1978" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1979" s="1">
+        <v>46226.649930555555</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1979" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1979">
+        <v>2782836519</v>
+      </c>
+      <c r="G1979" s="2">
+        <v>1784831704760810</v>
+      </c>
+      <c r="H1979" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1979" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1979" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1979" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1979" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1979">
+        <v>19</v>
+      </c>
+      <c r="R1979" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1979" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1980" s="1">
+        <v>46226.650266203702</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1980" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1980">
+        <v>2752537906</v>
+      </c>
+      <c r="G1980" s="2">
+        <v>1784831783763650</v>
+      </c>
+      <c r="H1980" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1980" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1980" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1980" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1980" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1980">
+        <v>19</v>
+      </c>
+      <c r="R1980" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1980" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1981" s="1">
+        <v>46226.650972222225</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1981" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1981">
+        <v>2784185013</v>
+      </c>
+      <c r="G1981" s="2">
+        <v>1784831844765820</v>
+      </c>
+      <c r="H1981" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1981" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1981" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1981" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1981" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1981">
+        <v>19</v>
+      </c>
+      <c r="R1981" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1981" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1982" s="1">
+        <v>46226.651446759257</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1982" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1982">
+        <v>2784185054</v>
+      </c>
+      <c r="G1982" s="2">
+        <v>1784831885766730</v>
+      </c>
+      <c r="H1982" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1982" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1982" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1982" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1982" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1982">
+        <v>19</v>
+      </c>
+      <c r="R1982" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1982" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1983" s="1">
+        <v>46226.651817129627</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1983" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1983">
+        <v>2784185086</v>
+      </c>
+      <c r="G1983" s="2">
+        <v>1784831917767670</v>
+      </c>
+      <c r="H1983" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1983" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1983" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1983" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1983" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1983" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1983">
+        <v>16</v>
+      </c>
+      <c r="R1983" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1983" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1984" s="1">
+        <v>46226.652175925927</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1984" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1984">
+        <v>2784185117</v>
+      </c>
+      <c r="G1984" s="2">
+        <v>1784831948768730</v>
+      </c>
+      <c r="H1984" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1984" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1984" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1984" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1984" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1984" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1984">
+        <v>16</v>
+      </c>
+      <c r="R1984" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S1984" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1985" s="1">
+        <v>46226.65253472222</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1985" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1985">
+        <v>2784185148</v>
+      </c>
+      <c r="G1985" s="2">
+        <v>1784831979769520</v>
+      </c>
+      <c r="H1985" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1985" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1985" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1985" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1985" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1985" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1985">
+        <v>16</v>
+      </c>
+      <c r="R1985" s="3">
+        <v>4.6412037037037038E-3</v>
+      </c>
+      <c r="S1985" s="3">
+        <v>4.4560185185185189E-3</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1986" s="1">
+        <v>46226.659131944441</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1986" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1986">
+        <v>2756063359</v>
+      </c>
+      <c r="G1986" s="2">
+        <v>1784832549784060</v>
+      </c>
+      <c r="H1986" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1986" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1986" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1986" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1986" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1986">
+        <v>19</v>
+      </c>
+      <c r="R1986" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S1986" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1987" s="1">
+        <v>46226.668310185189</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1987" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1987">
+        <v>2775270468</v>
+      </c>
+      <c r="G1987" s="2">
+        <v>1784833342809270</v>
+      </c>
+      <c r="H1987" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1987" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1987" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1987" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1987" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1987" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1987">
+        <v>16</v>
+      </c>
+      <c r="R1987" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S1987" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1988" s="1">
+        <v>46226.668773148151</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1988" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1988">
+        <v>1819332403</v>
+      </c>
+      <c r="G1988" s="2">
+        <v>1784833382810460</v>
+      </c>
+      <c r="H1988" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1988" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1988" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1988" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1988" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1988" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1988">
+        <v>16</v>
+      </c>
+      <c r="R1988" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="S1988" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1989" s="1">
+        <v>46226.670949074076</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1989" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1989">
+        <v>2784672048</v>
+      </c>
+      <c r="G1989" s="2">
+        <v>1784833520814850</v>
+      </c>
+      <c r="H1989" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1989" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1989" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1989" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1989" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1989">
+        <v>19</v>
+      </c>
+      <c r="R1989" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1989" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1990" s="1">
+        <v>46226.673576388886</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1990" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1990">
+        <v>2784672325</v>
+      </c>
+      <c r="G1990" s="2">
+        <v>1784833797823820</v>
+      </c>
+      <c r="H1990" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1990" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1990" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1990" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1990" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1990">
+        <v>19</v>
+      </c>
+      <c r="R1990" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1990" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1991" s="1">
+        <v>46226.675613425927</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1991" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1991">
+        <v>2777346278</v>
+      </c>
+      <c r="G1991" s="2">
+        <v>1784833973828560</v>
+      </c>
+      <c r="H1991" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1991" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1991" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1991" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1991" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1991">
+        <v>19</v>
+      </c>
+      <c r="R1991" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S1991" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1992" s="1">
+        <v>46226.677534722221</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1992" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1992">
+        <v>2777806341</v>
+      </c>
+      <c r="G1992" s="2">
+        <v>1784834139833350</v>
+      </c>
+      <c r="H1992" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1992" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1992" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1992" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1992" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1992">
+        <v>19</v>
+      </c>
+      <c r="R1992" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S1992" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1993" s="1">
+        <v>46226.677905092591</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1993" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1993">
+        <v>2777806373</v>
+      </c>
+      <c r="G1993" s="2">
+        <v>1784834171834430</v>
+      </c>
+      <c r="H1993" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1993" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1993" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1993" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1993" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1993">
+        <v>19</v>
+      </c>
+      <c r="R1993" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1993" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1994" s="1">
+        <v>46226.678738425922</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1994" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1994">
+        <v>2765975001</v>
+      </c>
+      <c r="G1994" s="2">
+        <v>1784834243836940</v>
+      </c>
+      <c r="H1994" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1994" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1994" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1994" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1994" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1994" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1994">
+        <v>16</v>
+      </c>
+      <c r="R1994" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1994" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1995" s="1">
+        <v>46226.678946759261</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1995" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1995">
+        <v>2765975019</v>
+      </c>
+      <c r="G1995" s="2">
+        <v>1784834261837870</v>
+      </c>
+      <c r="H1995" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1995" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1995" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1995" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1995" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1995" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1995">
+        <v>16</v>
+      </c>
+      <c r="R1995" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1995" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1996" s="1">
+        <v>46226.679409722223</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1996" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1996">
+        <v>2777712773</v>
+      </c>
+      <c r="G1996" s="2">
+        <v>1784834301839390</v>
+      </c>
+      <c r="H1996" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1996" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1996" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1996" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1996" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1996">
+        <v>19</v>
+      </c>
+      <c r="R1996" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1996" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1997" s="1">
+        <v>46226.680254629631</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1997" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1997">
+        <v>2778352712</v>
+      </c>
+      <c r="G1997" s="2">
+        <v>1784834374842780</v>
+      </c>
+      <c r="H1997" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1997" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1997" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1997" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1997" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1997">
+        <v>19</v>
+      </c>
+      <c r="R1997" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1997" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1998" s="1">
+        <v>46226.680671296293</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1998" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1998">
+        <v>1822824734</v>
+      </c>
+      <c r="G1998" s="2">
+        <v>1784834410844140</v>
+      </c>
+      <c r="H1998" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1998" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1998" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1998" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1998" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1998">
+        <v>19</v>
+      </c>
+      <c r="R1998" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1998" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1999" s="1">
+        <v>46226.681273148148</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1999" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1999">
+        <v>2777073467</v>
+      </c>
+      <c r="G1999" s="2">
+        <v>1784834462846120</v>
+      </c>
+      <c r="H1999" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1999" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1999" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1999" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1999" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1999">
+        <v>19</v>
+      </c>
+      <c r="R1999" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1999" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2000" s="1">
+        <v>46226.681446759256</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2000" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2000">
+        <v>2777073482</v>
+      </c>
+      <c r="G2000" s="2">
+        <v>1784834477846810</v>
+      </c>
+      <c r="H2000" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2000" t="s">
+        <v>137</v>
+      </c>
+      <c r="J2000" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2000" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2000" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2000">
+        <v>19</v>
+      </c>
+      <c r="R2000" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S2000" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2001" s="1">
+        <v>46226.681863425925</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2001" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2001">
+        <v>2773316342</v>
+      </c>
+      <c r="G2001" s="2">
+        <v>1784834513848490</v>
+      </c>
+      <c r="H2001" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2001" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2001" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2001" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2001" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2001" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2001">
+        <v>16</v>
+      </c>
+      <c r="R2001" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S2001" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2002" s="1">
+        <v>46226.682488425926</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2002" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2002">
+        <v>2772245790</v>
+      </c>
+      <c r="G2002" s="2">
+        <v>1784834567850700</v>
+      </c>
+      <c r="H2002" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2002" t="s">
+        <v>136</v>
+      </c>
+      <c r="J2002" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2002" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2002" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2002">
+        <v>19</v>
+      </c>
+      <c r="R2002" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S2002" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2003" s="1">
+        <v>46226.682638888888</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2003" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2003">
+        <v>2772245803</v>
+      </c>
+      <c r="G2003" s="2">
+        <v>1784834580851160</v>
+      </c>
+      <c r="H2003" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2003" t="s">
+        <v>136</v>
+      </c>
+      <c r="J2003" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2003" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2003" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2003">
+        <v>19</v>
+      </c>
+      <c r="R2003" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S2003" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2004" s="1">
+        <v>46226.709699074076</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2004" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2004">
+        <v>2775274044</v>
+      </c>
+      <c r="G2004" s="2">
+        <v>1784836918927530</v>
+      </c>
+      <c r="H2004" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2004" t="s">
+        <v>148</v>
+      </c>
+      <c r="J2004" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2004" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2004" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2004" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2004">
+        <v>16</v>
+      </c>
+      <c r="R2004" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S2004" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2005" s="1">
+        <v>46226.710057870368</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2005" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2005">
+        <v>2775274075</v>
+      </c>
+      <c r="G2005" s="2">
+        <v>1784836949928880</v>
+      </c>
+      <c r="H2005" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2005" t="s">
+        <v>148</v>
+      </c>
+      <c r="J2005" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2005" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2005" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2005" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2005">
+        <v>16</v>
+      </c>
+      <c r="R2005" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S2005" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2006" s="1">
+        <v>46226.710949074077</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2006" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2006">
+        <v>1819336017</v>
+      </c>
+      <c r="G2006" s="2">
+        <v>1784836996930280</v>
+      </c>
+      <c r="H2006" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2006" t="s">
+        <v>149</v>
+      </c>
+      <c r="J2006" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2006" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2006" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2006">
+        <v>19</v>
+      </c>
+      <c r="R2006" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S2006" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2007" s="1">
+        <v>46226.711446759262</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2007" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2007">
+        <v>1819336059</v>
+      </c>
+      <c r="G2007" s="2">
+        <v>1784837038931840</v>
+      </c>
+      <c r="H2007" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2007" t="s">
+        <v>149</v>
+      </c>
+      <c r="J2007" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2007" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2007" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2007">
+        <v>19</v>
+      </c>
+      <c r="R2007" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S2007" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
